--- a/[학원실습용] 전투 및 스테이지 요소 있는 버전 - 넌 착해 게임 밸런스 기획서.xlsx
+++ b/[학원실습용] 전투 및 스테이지 요소 있는 버전 - 넌 착해 게임 밸런스 기획서.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="1063">
   <si>
     <t>2/10 – 등장 인물 수·장면 전환 속도·결과 연결성이 난이도를 결정함</t>
   </si>
@@ -3190,6 +3190,38 @@
   </si>
   <si>
     <t>—</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스가 주는 경험치</t>
+  </si>
+  <si>
+    <t>해당 레벨의
+보스 분포 수</t>
+  </si>
+  <si>
+    <t>보스 잡는 데 걸리는 시간(초)
+보스타입 (근거리)</t>
+  </si>
+  <si>
+    <t>보스 잡는 데 걸리는 시간(초)
+보스타입 (원거리)</t>
+  </si>
+  <si>
+    <t>퀘스트의 레벨별 분포</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 플레이 시간(초)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 보상 경험치량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kill 이벤트
+(관문)</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3200,7 +3232,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3264,8 +3296,24 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF7F6000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3290,8 +3338,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF334E68"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -3445,6 +3503,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3458,7 +3544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3626,6 +3712,30 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9916,7 +10026,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AJ153"/>
+  <dimension ref="A1:AM178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" style="39" customWidth="1"/>
@@ -9949,7 +10059,7 @@
     <col min="37" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="36.75" customHeight="1">
+    <row r="1" spans="1:39" ht="36.75" customHeight="1">
       <c r="Q1" s="39" t="s">
         <v>531</v>
       </c>
@@ -9957,7 +10067,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="36.75" customHeight="1">
+    <row r="2" spans="1:39" ht="36.75" customHeight="1">
       <c r="M2" s="41" t="s">
         <v>522</v>
       </c>
@@ -9968,7 +10078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="33.950000000000003" customHeight="1">
+    <row r="3" spans="1:39" ht="33.950000000000003" customHeight="1">
       <c r="Q3" s="42">
         <f>Q2/100</f>
         <v>9.8499999999999994E-3</v>
@@ -9997,7 +10107,7 @@
       <c r="AD3" s="64"/>
       <c r="AE3" s="65"/>
     </row>
-    <row r="4" spans="1:36" ht="42" customHeight="1">
+    <row r="4" spans="1:39" ht="42" customHeight="1">
       <c r="A4" s="59" t="s">
         <v>529</v>
       </c>
@@ -10091,13 +10201,32 @@
       <c r="AE4" s="62" t="s">
         <v>520</v>
       </c>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="41"/>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="41"/>
-    </row>
-    <row r="5" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF4" s="68" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AG4" s="68" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AH4" s="68" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AI4" s="68" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AJ4" s="69" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AK4" s="68" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AL4" s="68" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AM4" s="69" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A5" s="41" t="s">
         <v>892</v>
       </c>
@@ -10191,13 +10320,16 @@
       <c r="AE5" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="41"/>
-    </row>
-    <row r="6" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF5" s="70"/>
+      <c r="AG5" s="70"/>
+      <c r="AH5" s="70"/>
+      <c r="AI5" s="70"/>
+      <c r="AJ5" s="70"/>
+      <c r="AK5" s="70"/>
+      <c r="AL5" s="70"/>
+      <c r="AM5" s="71"/>
+    </row>
+    <row r="6" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A6" s="41" t="s">
         <v>892</v>
       </c>
@@ -10291,13 +10423,16 @@
       <c r="AE6" s="56">
         <v>2.199074074074074E-4</v>
       </c>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="41"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="41"/>
-      <c r="AJ6" s="41"/>
-    </row>
-    <row r="7" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF6" s="72"/>
+      <c r="AG6" s="72"/>
+      <c r="AH6" s="72"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="72"/>
+      <c r="AK6" s="72"/>
+      <c r="AL6" s="72"/>
+      <c r="AM6" s="73"/>
+    </row>
+    <row r="7" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A7" s="41" t="s">
         <v>892</v>
       </c>
@@ -10392,13 +10527,16 @@
       <c r="AE7" s="56">
         <v>6.5972222222222224E-4</v>
       </c>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-    </row>
-    <row r="8" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF7" s="72"/>
+      <c r="AG7" s="72"/>
+      <c r="AH7" s="72"/>
+      <c r="AI7" s="72"/>
+      <c r="AJ7" s="72"/>
+      <c r="AK7" s="72"/>
+      <c r="AL7" s="72"/>
+      <c r="AM7" s="73"/>
+    </row>
+    <row r="8" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A8" s="41" t="s">
         <v>892</v>
       </c>
@@ -10493,13 +10631,16 @@
       <c r="AE8" s="56">
         <v>4.3981481481481481E-4</v>
       </c>
-      <c r="AF8" s="41"/>
-      <c r="AG8" s="41"/>
-      <c r="AH8" s="41"/>
-      <c r="AI8" s="41"/>
-      <c r="AJ8" s="41"/>
-    </row>
-    <row r="9" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF8" s="72"/>
+      <c r="AG8" s="72"/>
+      <c r="AH8" s="72"/>
+      <c r="AI8" s="72"/>
+      <c r="AJ8" s="72"/>
+      <c r="AK8" s="72"/>
+      <c r="AL8" s="72"/>
+      <c r="AM8" s="73"/>
+    </row>
+    <row r="9" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A9" s="41" t="s">
         <v>892</v>
       </c>
@@ -10594,13 +10735,16 @@
       <c r="AE9" s="56">
         <v>3.2986111111111112E-4</v>
       </c>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="41"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-    </row>
-    <row r="10" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF9" s="72"/>
+      <c r="AG9" s="72"/>
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="72"/>
+      <c r="AJ9" s="72"/>
+      <c r="AK9" s="72"/>
+      <c r="AL9" s="72"/>
+      <c r="AM9" s="73"/>
+    </row>
+    <row r="10" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A10" s="41" t="s">
         <v>892</v>
       </c>
@@ -10695,13 +10839,16 @@
       <c r="AE10" s="56">
         <v>2.199074074074074E-4</v>
       </c>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="41"/>
-    </row>
-    <row r="11" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="72"/>
+      <c r="AL10" s="72"/>
+      <c r="AM10" s="73"/>
+    </row>
+    <row r="11" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A11" s="41" t="s">
         <v>892</v>
       </c>
@@ -10796,13 +10943,16 @@
       <c r="AE11" s="56">
         <v>8.2465277777777767E-4</v>
       </c>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="41"/>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="41"/>
-    </row>
-    <row r="12" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF11" s="72"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="72"/>
+      <c r="AI11" s="72"/>
+      <c r="AJ11" s="72"/>
+      <c r="AK11" s="72"/>
+      <c r="AL11" s="72"/>
+      <c r="AM11" s="73"/>
+    </row>
+    <row r="12" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A12" s="41" t="s">
         <v>892</v>
       </c>
@@ -10900,13 +11050,16 @@
       <c r="AE12" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="41"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="41"/>
-    </row>
-    <row r="13" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF12" s="72"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="72"/>
+      <c r="AJ12" s="72"/>
+      <c r="AK12" s="72"/>
+      <c r="AL12" s="72"/>
+      <c r="AM12" s="73"/>
+    </row>
+    <row r="13" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A13" s="41" t="s">
         <v>892</v>
       </c>
@@ -11004,13 +11157,16 @@
       <c r="AE13" s="56">
         <v>3.8483796296296291E-4</v>
       </c>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="41"/>
-      <c r="AJ13" s="41"/>
-    </row>
-    <row r="14" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF13" s="72"/>
+      <c r="AG13" s="72"/>
+      <c r="AH13" s="72"/>
+      <c r="AI13" s="72"/>
+      <c r="AJ13" s="72"/>
+      <c r="AK13" s="72"/>
+      <c r="AL13" s="72"/>
+      <c r="AM13" s="73"/>
+    </row>
+    <row r="14" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A14" s="41" t="s">
         <v>892</v>
       </c>
@@ -11105,13 +11261,16 @@
       <c r="AE14" s="56">
         <v>8.2465277777777767E-4</v>
       </c>
-      <c r="AF14" s="41"/>
-      <c r="AG14" s="41"/>
-      <c r="AH14" s="41"/>
-      <c r="AI14" s="41"/>
-      <c r="AJ14" s="41"/>
-    </row>
-    <row r="15" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="72"/>
+      <c r="AL14" s="72"/>
+      <c r="AM14" s="73"/>
+    </row>
+    <row r="15" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A15" s="41" t="s">
         <v>892</v>
       </c>
@@ -11206,13 +11365,16 @@
       <c r="AE15" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="41"/>
-    </row>
-    <row r="16" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="72"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="73"/>
+    </row>
+    <row r="16" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A16" s="41" t="s">
         <v>892</v>
       </c>
@@ -11310,13 +11472,16 @@
       <c r="AE16" s="56">
         <v>1.2094907407407408E-3</v>
       </c>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="41"/>
-    </row>
-    <row r="17" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
+      <c r="AL16" s="72"/>
+      <c r="AM16" s="73"/>
+    </row>
+    <row r="17" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A17" s="41" t="s">
         <v>892</v>
       </c>
@@ -11411,13 +11576,16 @@
       <c r="AE17" s="56">
         <v>5.4976851851851844E-4</v>
       </c>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="41"/>
-    </row>
-    <row r="18" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF17" s="72"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="72"/>
+      <c r="AL17" s="72"/>
+      <c r="AM17" s="73"/>
+    </row>
+    <row r="18" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A18" s="41" t="s">
         <v>892</v>
       </c>
@@ -11512,13 +11680,16 @@
       <c r="AE18" s="56">
         <v>1.3194444444444445E-3</v>
       </c>
-      <c r="AF18" s="41"/>
-      <c r="AG18" s="41"/>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="41"/>
-      <c r="AJ18" s="41"/>
-    </row>
-    <row r="19" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF18" s="72"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
+      <c r="AJ18" s="72"/>
+      <c r="AK18" s="72"/>
+      <c r="AL18" s="72"/>
+      <c r="AM18" s="73"/>
+    </row>
+    <row r="19" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A19" s="41" t="s">
         <v>892</v>
       </c>
@@ -11613,13 +11784,16 @@
       <c r="AE19" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="41"/>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="41"/>
-    </row>
-    <row r="20" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF19" s="72"/>
+      <c r="AG19" s="72"/>
+      <c r="AH19" s="72"/>
+      <c r="AI19" s="72"/>
+      <c r="AJ19" s="72"/>
+      <c r="AK19" s="72"/>
+      <c r="AL19" s="72"/>
+      <c r="AM19" s="73"/>
+    </row>
+    <row r="20" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A20" s="41" t="s">
         <v>892</v>
       </c>
@@ -11717,13 +11891,16 @@
       <c r="AE20" s="56">
         <v>2.7488425925925922E-4</v>
       </c>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="41"/>
-    </row>
-    <row r="21" spans="1:36" ht="52.7" customHeight="1">
+      <c r="AF20" s="72"/>
+      <c r="AG20" s="72"/>
+      <c r="AH20" s="72"/>
+      <c r="AI20" s="72"/>
+      <c r="AJ20" s="72"/>
+      <c r="AK20" s="72"/>
+      <c r="AL20" s="72"/>
+      <c r="AM20" s="73"/>
+    </row>
+    <row r="21" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A21" s="41" t="s">
         <v>892</v>
       </c>
@@ -11821,13 +11998,16 @@
       <c r="AE21" s="56">
         <v>7.4942129629629621E-4</v>
       </c>
-      <c r="AF21" s="41"/>
-      <c r="AG21" s="41"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="41"/>
-    </row>
-    <row r="22" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
+      <c r="AL21" s="72"/>
+      <c r="AM21" s="73"/>
+    </row>
+    <row r="22" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A22" s="41" t="s">
         <v>892</v>
       </c>
@@ -11925,13 +12105,16 @@
       <c r="AE22" s="56">
         <v>1.2152777777777778E-3</v>
       </c>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
-      <c r="AH22" s="41"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="41"/>
-    </row>
-    <row r="23" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
+      <c r="AL22" s="72"/>
+      <c r="AM22" s="73"/>
+    </row>
+    <row r="23" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A23" s="41" t="s">
         <v>892</v>
       </c>
@@ -12027,13 +12210,16 @@
       <c r="AE23" s="56">
         <v>8.1018518518518527E-4</v>
       </c>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="41"/>
-      <c r="AH23" s="41"/>
-      <c r="AI23" s="41"/>
-      <c r="AJ23" s="41"/>
-    </row>
-    <row r="24" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
+      <c r="AL23" s="72"/>
+      <c r="AM23" s="73"/>
+    </row>
+    <row r="24" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A24" s="41" t="s">
         <v>892</v>
       </c>
@@ -12131,13 +12317,16 @@
       <c r="AE24" s="56">
         <v>1.0416666666666664E-3</v>
       </c>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="41"/>
-    </row>
-    <row r="25" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
+      <c r="AL24" s="72"/>
+      <c r="AM24" s="73"/>
+    </row>
+    <row r="25" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A25" s="41" t="s">
         <v>892</v>
       </c>
@@ -12232,13 +12421,16 @@
       <c r="AE25" s="56">
         <v>6.047453703703704E-4</v>
       </c>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="41"/>
-      <c r="AJ25" s="41"/>
-    </row>
-    <row r="26" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF25" s="72"/>
+      <c r="AG25" s="72"/>
+      <c r="AH25" s="72"/>
+      <c r="AI25" s="72"/>
+      <c r="AJ25" s="72"/>
+      <c r="AK25" s="72"/>
+      <c r="AL25" s="72"/>
+      <c r="AM25" s="73"/>
+    </row>
+    <row r="26" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A26" s="41" t="s">
         <v>892</v>
       </c>
@@ -12333,13 +12525,16 @@
       <c r="AE26" s="56">
         <v>7.6967592592592582E-4</v>
       </c>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="41"/>
-    </row>
-    <row r="27" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF26" s="72"/>
+      <c r="AG26" s="72"/>
+      <c r="AH26" s="72"/>
+      <c r="AI26" s="72"/>
+      <c r="AJ26" s="72"/>
+      <c r="AK26" s="72"/>
+      <c r="AL26" s="72"/>
+      <c r="AM26" s="73"/>
+    </row>
+    <row r="27" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A27" s="41" t="s">
         <v>892</v>
       </c>
@@ -12436,13 +12631,16 @@
       <c r="AE27" s="56">
         <v>1.6493055555555553E-3</v>
       </c>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="41"/>
-      <c r="AJ27" s="41"/>
-    </row>
-    <row r="28" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF27" s="72"/>
+      <c r="AG27" s="72"/>
+      <c r="AH27" s="72"/>
+      <c r="AI27" s="72"/>
+      <c r="AJ27" s="72"/>
+      <c r="AK27" s="72"/>
+      <c r="AL27" s="72"/>
+      <c r="AM27" s="73"/>
+    </row>
+    <row r="28" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A28" s="41" t="s">
         <v>892</v>
       </c>
@@ -12540,13 +12738,16 @@
       <c r="AE28" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="41"/>
-    </row>
-    <row r="29" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF28" s="72"/>
+      <c r="AG28" s="72"/>
+      <c r="AH28" s="72"/>
+      <c r="AI28" s="72"/>
+      <c r="AJ28" s="72"/>
+      <c r="AK28" s="72"/>
+      <c r="AL28" s="72"/>
+      <c r="AM28" s="73"/>
+    </row>
+    <row r="29" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A29" s="41" t="s">
         <v>892</v>
       </c>
@@ -12644,13 +12845,16 @@
       <c r="AE29" s="56">
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="41"/>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="41"/>
-    </row>
-    <row r="30" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF29" s="72"/>
+      <c r="AG29" s="72"/>
+      <c r="AH29" s="72"/>
+      <c r="AI29" s="72"/>
+      <c r="AJ29" s="72"/>
+      <c r="AK29" s="72"/>
+      <c r="AL29" s="72"/>
+      <c r="AM29" s="73"/>
+    </row>
+    <row r="30" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A30" s="41" t="s">
         <v>892</v>
       </c>
@@ -12745,13 +12949,16 @@
       <c r="AE30" s="56">
         <v>7.1469907407407409E-4</v>
       </c>
-      <c r="AF30" s="41"/>
-      <c r="AG30" s="41"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="41"/>
-    </row>
-    <row r="31" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="72"/>
+      <c r="AH30" s="72"/>
+      <c r="AI30" s="72"/>
+      <c r="AJ30" s="72"/>
+      <c r="AK30" s="72"/>
+      <c r="AL30" s="72"/>
+      <c r="AM30" s="73"/>
+    </row>
+    <row r="31" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A31" s="41" t="s">
         <v>892</v>
       </c>
@@ -12846,13 +13053,16 @@
       <c r="AE31" s="56">
         <v>1.2094907407407408E-3</v>
       </c>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="41"/>
-    </row>
-    <row r="32" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF31" s="72"/>
+      <c r="AG31" s="72"/>
+      <c r="AH31" s="72"/>
+      <c r="AI31" s="72"/>
+      <c r="AJ31" s="72"/>
+      <c r="AK31" s="72"/>
+      <c r="AL31" s="72"/>
+      <c r="AM31" s="73"/>
+    </row>
+    <row r="32" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A32" s="41" t="s">
         <v>928</v>
       </c>
@@ -12950,13 +13160,16 @@
       <c r="AE32" s="56">
         <v>8.2465277777777767E-4</v>
       </c>
-      <c r="AF32" s="41"/>
-      <c r="AG32" s="41"/>
-      <c r="AH32" s="41"/>
-      <c r="AI32" s="41"/>
-      <c r="AJ32" s="41"/>
-    </row>
-    <row r="33" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF32" s="72"/>
+      <c r="AG32" s="72"/>
+      <c r="AH32" s="72"/>
+      <c r="AI32" s="72"/>
+      <c r="AJ32" s="72"/>
+      <c r="AK32" s="72"/>
+      <c r="AL32" s="72"/>
+      <c r="AM32" s="73"/>
+    </row>
+    <row r="33" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A33" s="41" t="s">
         <v>928</v>
       </c>
@@ -13051,13 +13264,16 @@
       <c r="AE33" s="56">
         <v>3.8483796296296291E-4</v>
       </c>
-      <c r="AF33" s="41"/>
-      <c r="AG33" s="41"/>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="41"/>
-    </row>
-    <row r="34" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF33" s="72"/>
+      <c r="AG33" s="72"/>
+      <c r="AH33" s="72"/>
+      <c r="AI33" s="72"/>
+      <c r="AJ33" s="72"/>
+      <c r="AK33" s="72"/>
+      <c r="AL33" s="72"/>
+      <c r="AM33" s="73"/>
+    </row>
+    <row r="34" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A34" s="41" t="s">
         <v>928</v>
       </c>
@@ -13152,13 +13368,16 @@
       <c r="AE34" s="56">
         <v>4.947916666666666E-4</v>
       </c>
-      <c r="AF34" s="41"/>
-      <c r="AG34" s="41"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="41"/>
-      <c r="AJ34" s="41"/>
-    </row>
-    <row r="35" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF34" s="72"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="72"/>
+      <c r="AI34" s="72"/>
+      <c r="AJ34" s="72"/>
+      <c r="AK34" s="72"/>
+      <c r="AL34" s="72"/>
+      <c r="AM34" s="73"/>
+    </row>
+    <row r="35" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A35" s="41" t="s">
         <v>928</v>
       </c>
@@ -13256,13 +13475,16 @@
       <c r="AE35" s="56">
         <v>9.3460648148148136E-4</v>
       </c>
-      <c r="AF35" s="41"/>
-      <c r="AG35" s="41"/>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="41"/>
-      <c r="AJ35" s="41"/>
-    </row>
-    <row r="36" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF35" s="72"/>
+      <c r="AG35" s="72"/>
+      <c r="AH35" s="72"/>
+      <c r="AI35" s="72"/>
+      <c r="AJ35" s="72"/>
+      <c r="AK35" s="72"/>
+      <c r="AL35" s="72"/>
+      <c r="AM35" s="73"/>
+    </row>
+    <row r="36" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A36" s="41" t="s">
         <v>928</v>
       </c>
@@ -13360,13 +13582,16 @@
       <c r="AE36" s="56">
         <v>8.3333333333333328E-4</v>
       </c>
-      <c r="AF36" s="41"/>
-      <c r="AG36" s="41"/>
-      <c r="AH36" s="41"/>
-      <c r="AI36" s="41"/>
-      <c r="AJ36" s="41"/>
-    </row>
-    <row r="37" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF36" s="72"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="72"/>
+      <c r="AJ36" s="72"/>
+      <c r="AK36" s="72"/>
+      <c r="AL36" s="72"/>
+      <c r="AM36" s="73"/>
+    </row>
+    <row r="37" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A37" s="41" t="s">
         <v>928</v>
       </c>
@@ -13461,13 +13686,16 @@
       <c r="AE37" s="56">
         <v>6.047453703703704E-4</v>
       </c>
-      <c r="AF37" s="41"/>
-      <c r="AG37" s="41"/>
-      <c r="AH37" s="41"/>
-      <c r="AI37" s="41"/>
-      <c r="AJ37" s="41"/>
-    </row>
-    <row r="38" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF37" s="72"/>
+      <c r="AG37" s="72"/>
+      <c r="AH37" s="72"/>
+      <c r="AI37" s="72"/>
+      <c r="AJ37" s="72"/>
+      <c r="AK37" s="72"/>
+      <c r="AL37" s="72"/>
+      <c r="AM37" s="73"/>
+    </row>
+    <row r="38" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A38" s="41" t="s">
         <v>928</v>
       </c>
@@ -13565,13 +13793,16 @@
       <c r="AE38" s="56">
         <v>1.9791666666666664E-3</v>
       </c>
-      <c r="AF38" s="41"/>
-      <c r="AG38" s="41"/>
-      <c r="AH38" s="41"/>
-      <c r="AI38" s="41"/>
-      <c r="AJ38" s="41"/>
-    </row>
-    <row r="39" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF38" s="72"/>
+      <c r="AG38" s="72"/>
+      <c r="AH38" s="72"/>
+      <c r="AI38" s="72"/>
+      <c r="AJ38" s="72"/>
+      <c r="AK38" s="72"/>
+      <c r="AL38" s="72"/>
+      <c r="AM38" s="73"/>
+    </row>
+    <row r="39" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A39" s="41" t="s">
         <v>928</v>
       </c>
@@ -13669,13 +13900,16 @@
       <c r="AE39" s="56">
         <v>1.7592592592592592E-3</v>
       </c>
-      <c r="AF39" s="41"/>
-      <c r="AG39" s="41"/>
-      <c r="AH39" s="41"/>
-      <c r="AI39" s="41"/>
-      <c r="AJ39" s="41"/>
-    </row>
-    <row r="40" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF39" s="72"/>
+      <c r="AG39" s="72"/>
+      <c r="AH39" s="72"/>
+      <c r="AI39" s="72"/>
+      <c r="AJ39" s="72"/>
+      <c r="AK39" s="72"/>
+      <c r="AL39" s="72"/>
+      <c r="AM39" s="73"/>
+    </row>
+    <row r="40" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A40" s="41" t="s">
         <v>928</v>
       </c>
@@ -13773,13 +14007,16 @@
       <c r="AE40" s="56">
         <v>1.6059027777777775E-3</v>
       </c>
-      <c r="AF40" s="41"/>
-      <c r="AG40" s="41"/>
-      <c r="AH40" s="41"/>
-      <c r="AI40" s="41"/>
-      <c r="AJ40" s="41"/>
-    </row>
-    <row r="41" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF40" s="72"/>
+      <c r="AG40" s="72"/>
+      <c r="AH40" s="72"/>
+      <c r="AI40" s="72"/>
+      <c r="AJ40" s="72"/>
+      <c r="AK40" s="72"/>
+      <c r="AL40" s="72"/>
+      <c r="AM40" s="73"/>
+    </row>
+    <row r="41" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A41" s="41" t="s">
         <v>928</v>
       </c>
@@ -13874,13 +14111,16 @@
       <c r="AE41" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="41"/>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="41"/>
-      <c r="AJ41" s="41"/>
-    </row>
-    <row r="42" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF41" s="72"/>
+      <c r="AG41" s="72"/>
+      <c r="AH41" s="72"/>
+      <c r="AI41" s="72"/>
+      <c r="AJ41" s="72"/>
+      <c r="AK41" s="72"/>
+      <c r="AL41" s="72"/>
+      <c r="AM41" s="73"/>
+    </row>
+    <row r="42" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A42" s="41" t="s">
         <v>928</v>
       </c>
@@ -13975,13 +14215,16 @@
       <c r="AE42" s="56">
         <v>1.5393518518518516E-3</v>
       </c>
-      <c r="AF42" s="41"/>
-      <c r="AG42" s="41"/>
-      <c r="AH42" s="41"/>
-      <c r="AI42" s="41"/>
-      <c r="AJ42" s="41"/>
-    </row>
-    <row r="43" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF42" s="72"/>
+      <c r="AG42" s="72"/>
+      <c r="AH42" s="72"/>
+      <c r="AI42" s="72"/>
+      <c r="AJ42" s="72"/>
+      <c r="AK42" s="72"/>
+      <c r="AL42" s="72"/>
+      <c r="AM42" s="73"/>
+    </row>
+    <row r="43" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A43" s="41" t="s">
         <v>928</v>
       </c>
@@ -14079,13 +14322,16 @@
       <c r="AE43" s="56">
         <v>1.25E-3</v>
       </c>
-      <c r="AF43" s="41"/>
-      <c r="AG43" s="41"/>
-      <c r="AH43" s="41"/>
-      <c r="AI43" s="41"/>
-      <c r="AJ43" s="41"/>
-    </row>
-    <row r="44" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF43" s="72"/>
+      <c r="AG43" s="72"/>
+      <c r="AH43" s="72"/>
+      <c r="AI43" s="72"/>
+      <c r="AJ43" s="72"/>
+      <c r="AK43" s="72"/>
+      <c r="AL43" s="72"/>
+      <c r="AM43" s="73"/>
+    </row>
+    <row r="44" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A44" s="41" t="s">
         <v>928</v>
       </c>
@@ -14183,13 +14429,16 @@
       <c r="AE44" s="56">
         <v>8.2465277777777767E-4</v>
       </c>
-      <c r="AF44" s="41"/>
-      <c r="AG44" s="41"/>
-      <c r="AH44" s="41"/>
-      <c r="AI44" s="41"/>
-      <c r="AJ44" s="41"/>
-    </row>
-    <row r="45" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF44" s="72"/>
+      <c r="AG44" s="72"/>
+      <c r="AH44" s="72"/>
+      <c r="AI44" s="72"/>
+      <c r="AJ44" s="72"/>
+      <c r="AK44" s="72"/>
+      <c r="AL44" s="72"/>
+      <c r="AM44" s="73"/>
+    </row>
+    <row r="45" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A45" s="41" t="s">
         <v>928</v>
       </c>
@@ -14287,13 +14536,16 @@
       <c r="AE45" s="56">
         <v>1.25E-3</v>
       </c>
-      <c r="AF45" s="41"/>
-      <c r="AG45" s="41"/>
-      <c r="AH45" s="41"/>
-      <c r="AI45" s="41"/>
-      <c r="AJ45" s="41"/>
-    </row>
-    <row r="46" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF45" s="72"/>
+      <c r="AG45" s="72"/>
+      <c r="AH45" s="72"/>
+      <c r="AI45" s="72"/>
+      <c r="AJ45" s="72"/>
+      <c r="AK45" s="72"/>
+      <c r="AL45" s="72"/>
+      <c r="AM45" s="73"/>
+    </row>
+    <row r="46" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A46" s="41" t="s">
         <v>928</v>
       </c>
@@ -14391,13 +14643,16 @@
       <c r="AE46" s="56">
         <v>1.8200231481481479E-3</v>
       </c>
-      <c r="AF46" s="41"/>
-      <c r="AG46" s="41"/>
-      <c r="AH46" s="41"/>
-      <c r="AI46" s="41"/>
-      <c r="AJ46" s="41"/>
-    </row>
-    <row r="47" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF46" s="72"/>
+      <c r="AG46" s="72"/>
+      <c r="AH46" s="72"/>
+      <c r="AI46" s="72"/>
+      <c r="AJ46" s="72"/>
+      <c r="AK46" s="72"/>
+      <c r="AL46" s="72"/>
+      <c r="AM46" s="73"/>
+    </row>
+    <row r="47" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A47" s="41" t="s">
         <v>928</v>
       </c>
@@ -14492,13 +14747,16 @@
       <c r="AE47" s="56">
         <v>7.6967592592592582E-4</v>
       </c>
-      <c r="AF47" s="41"/>
-      <c r="AG47" s="41"/>
-      <c r="AH47" s="41"/>
-      <c r="AI47" s="41"/>
-      <c r="AJ47" s="41"/>
-    </row>
-    <row r="48" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF47" s="72"/>
+      <c r="AG47" s="72"/>
+      <c r="AH47" s="72"/>
+      <c r="AI47" s="72"/>
+      <c r="AJ47" s="72"/>
+      <c r="AK47" s="72"/>
+      <c r="AL47" s="72"/>
+      <c r="AM47" s="73"/>
+    </row>
+    <row r="48" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A48" s="41" t="s">
         <v>928</v>
       </c>
@@ -14593,13 +14851,16 @@
       <c r="AE48" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF48" s="41"/>
-      <c r="AG48" s="41"/>
-      <c r="AH48" s="41"/>
-      <c r="AI48" s="41"/>
-      <c r="AJ48" s="41"/>
-    </row>
-    <row r="49" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF48" s="72"/>
+      <c r="AG48" s="72"/>
+      <c r="AH48" s="72"/>
+      <c r="AI48" s="72"/>
+      <c r="AJ48" s="72"/>
+      <c r="AK48" s="72"/>
+      <c r="AL48" s="72"/>
+      <c r="AM48" s="73"/>
+    </row>
+    <row r="49" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A49" s="41" t="s">
         <v>928</v>
       </c>
@@ -14694,13 +14955,16 @@
       <c r="AE49" s="56">
         <v>8.2465277777777767E-4</v>
       </c>
-      <c r="AF49" s="41"/>
-      <c r="AG49" s="41"/>
-      <c r="AH49" s="41"/>
-      <c r="AI49" s="41"/>
-      <c r="AJ49" s="41"/>
-    </row>
-    <row r="50" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF49" s="72"/>
+      <c r="AG49" s="72"/>
+      <c r="AH49" s="72"/>
+      <c r="AI49" s="72"/>
+      <c r="AJ49" s="72"/>
+      <c r="AK49" s="72"/>
+      <c r="AL49" s="72"/>
+      <c r="AM49" s="73"/>
+    </row>
+    <row r="50" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A50" s="41" t="s">
         <v>928</v>
       </c>
@@ -14798,13 +15062,16 @@
       <c r="AE50" s="56">
         <v>1.5393518518518516E-3</v>
       </c>
-      <c r="AF50" s="41"/>
-      <c r="AG50" s="41"/>
-      <c r="AH50" s="41"/>
-      <c r="AI50" s="41"/>
-      <c r="AJ50" s="41"/>
-    </row>
-    <row r="51" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF50" s="72"/>
+      <c r="AG50" s="72"/>
+      <c r="AH50" s="72"/>
+      <c r="AI50" s="72"/>
+      <c r="AJ50" s="72"/>
+      <c r="AK50" s="72"/>
+      <c r="AL50" s="72"/>
+      <c r="AM50" s="73"/>
+    </row>
+    <row r="51" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A51" s="41" t="s">
         <v>928</v>
       </c>
@@ -14902,13 +15169,16 @@
       <c r="AE51" s="56">
         <v>1.9270833333333332E-3</v>
       </c>
-      <c r="AF51" s="41"/>
-      <c r="AG51" s="41"/>
-      <c r="AH51" s="41"/>
-      <c r="AI51" s="41"/>
-      <c r="AJ51" s="41"/>
-    </row>
-    <row r="52" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF51" s="72"/>
+      <c r="AG51" s="72"/>
+      <c r="AH51" s="72"/>
+      <c r="AI51" s="72"/>
+      <c r="AJ51" s="72"/>
+      <c r="AK51" s="72"/>
+      <c r="AL51" s="72"/>
+      <c r="AM51" s="73"/>
+    </row>
+    <row r="52" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A52" s="41" t="s">
         <v>928</v>
       </c>
@@ -15006,13 +15276,16 @@
       <c r="AE52" s="56">
         <v>1.712962962962963E-3</v>
       </c>
-      <c r="AF52" s="41"/>
-      <c r="AG52" s="41"/>
-      <c r="AH52" s="41"/>
-      <c r="AI52" s="41"/>
-      <c r="AJ52" s="41"/>
-    </row>
-    <row r="53" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF52" s="72"/>
+      <c r="AG52" s="72"/>
+      <c r="AH52" s="72"/>
+      <c r="AI52" s="72"/>
+      <c r="AJ52" s="72"/>
+      <c r="AK52" s="72"/>
+      <c r="AL52" s="72"/>
+      <c r="AM52" s="73"/>
+    </row>
+    <row r="53" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A53" s="41" t="s">
         <v>928</v>
       </c>
@@ -15110,13 +15383,16 @@
       <c r="AE53" s="56">
         <v>1.0127314814814814E-3</v>
       </c>
-      <c r="AF53" s="41"/>
-      <c r="AG53" s="41"/>
-      <c r="AH53" s="41"/>
-      <c r="AI53" s="41"/>
-      <c r="AJ53" s="41"/>
-    </row>
-    <row r="54" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF53" s="72"/>
+      <c r="AG53" s="72"/>
+      <c r="AH53" s="72"/>
+      <c r="AI53" s="72"/>
+      <c r="AJ53" s="72"/>
+      <c r="AK53" s="72"/>
+      <c r="AL53" s="72"/>
+      <c r="AM53" s="73"/>
+    </row>
+    <row r="54" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A54" s="41" t="s">
         <v>928</v>
       </c>
@@ -15211,13 +15487,16 @@
       <c r="AE54" s="56">
         <v>7.6967592592592582E-4</v>
       </c>
-      <c r="AF54" s="41"/>
-      <c r="AG54" s="41"/>
-      <c r="AH54" s="41"/>
-      <c r="AI54" s="41"/>
-      <c r="AJ54" s="41"/>
-    </row>
-    <row r="55" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF54" s="72"/>
+      <c r="AG54" s="72"/>
+      <c r="AH54" s="72"/>
+      <c r="AI54" s="72"/>
+      <c r="AJ54" s="72"/>
+      <c r="AK54" s="72"/>
+      <c r="AL54" s="72"/>
+      <c r="AM54" s="73"/>
+    </row>
+    <row r="55" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A55" s="41" t="s">
         <v>928</v>
       </c>
@@ -15312,13 +15591,16 @@
       <c r="AE55" s="56">
         <v>5.4976851851851844E-4</v>
       </c>
-      <c r="AF55" s="41"/>
-      <c r="AG55" s="41"/>
-      <c r="AH55" s="41"/>
-      <c r="AI55" s="41"/>
-      <c r="AJ55" s="41"/>
-    </row>
-    <row r="56" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF55" s="72"/>
+      <c r="AG55" s="72"/>
+      <c r="AH55" s="72"/>
+      <c r="AI55" s="72"/>
+      <c r="AJ55" s="72"/>
+      <c r="AK55" s="72"/>
+      <c r="AL55" s="72"/>
+      <c r="AM55" s="73"/>
+    </row>
+    <row r="56" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A56" s="41" t="s">
         <v>928</v>
       </c>
@@ -15413,13 +15695,16 @@
       <c r="AE56" s="56">
         <v>1.0445601851851853E-3</v>
       </c>
-      <c r="AF56" s="41"/>
-      <c r="AG56" s="41"/>
-      <c r="AH56" s="41"/>
-      <c r="AI56" s="41"/>
-      <c r="AJ56" s="41"/>
-    </row>
-    <row r="57" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF56" s="72"/>
+      <c r="AG56" s="72"/>
+      <c r="AH56" s="72"/>
+      <c r="AI56" s="72"/>
+      <c r="AJ56" s="72"/>
+      <c r="AK56" s="72"/>
+      <c r="AL56" s="72"/>
+      <c r="AM56" s="73"/>
+    </row>
+    <row r="57" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A57" s="41" t="s">
         <v>928</v>
       </c>
@@ -15514,13 +15799,16 @@
       <c r="AE57" s="56">
         <v>1.3194444444444445E-3</v>
       </c>
-      <c r="AF57" s="41"/>
-      <c r="AG57" s="41"/>
-      <c r="AH57" s="41"/>
-      <c r="AI57" s="41"/>
-      <c r="AJ57" s="41"/>
-    </row>
-    <row r="58" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF57" s="72"/>
+      <c r="AG57" s="72"/>
+      <c r="AH57" s="72"/>
+      <c r="AI57" s="72"/>
+      <c r="AJ57" s="72"/>
+      <c r="AK57" s="72"/>
+      <c r="AL57" s="72"/>
+      <c r="AM57" s="73"/>
+    </row>
+    <row r="58" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A58" s="41" t="s">
         <v>928</v>
       </c>
@@ -15615,13 +15903,16 @@
       <c r="AE58" s="56">
         <v>3.8483796296296291E-4</v>
       </c>
-      <c r="AF58" s="41"/>
-      <c r="AG58" s="41"/>
-      <c r="AH58" s="41"/>
-      <c r="AI58" s="41"/>
-      <c r="AJ58" s="41"/>
-    </row>
-    <row r="59" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF58" s="72"/>
+      <c r="AG58" s="72"/>
+      <c r="AH58" s="72"/>
+      <c r="AI58" s="72"/>
+      <c r="AJ58" s="72"/>
+      <c r="AK58" s="72"/>
+      <c r="AL58" s="72"/>
+      <c r="AM58" s="73"/>
+    </row>
+    <row r="59" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A59" s="41" t="s">
         <v>935</v>
       </c>
@@ -15716,13 +16007,16 @@
       <c r="AE59" s="56">
         <v>4.3981481481481481E-4</v>
       </c>
-      <c r="AF59" s="41"/>
-      <c r="AG59" s="41"/>
-      <c r="AH59" s="41"/>
-      <c r="AI59" s="41"/>
-      <c r="AJ59" s="41"/>
-    </row>
-    <row r="60" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF59" s="72"/>
+      <c r="AG59" s="72"/>
+      <c r="AH59" s="72"/>
+      <c r="AI59" s="72"/>
+      <c r="AJ59" s="72"/>
+      <c r="AK59" s="72"/>
+      <c r="AL59" s="72"/>
+      <c r="AM59" s="73"/>
+    </row>
+    <row r="60" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A60" s="41" t="s">
         <v>935</v>
       </c>
@@ -15820,13 +16114,16 @@
       <c r="AE60" s="56">
         <v>7.6967592592592582E-4</v>
       </c>
-      <c r="AF60" s="41"/>
-      <c r="AG60" s="41"/>
-      <c r="AH60" s="41"/>
-      <c r="AI60" s="41"/>
-      <c r="AJ60" s="41"/>
-    </row>
-    <row r="61" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF60" s="72"/>
+      <c r="AG60" s="72"/>
+      <c r="AH60" s="72"/>
+      <c r="AI60" s="72"/>
+      <c r="AJ60" s="72"/>
+      <c r="AK60" s="72"/>
+      <c r="AL60" s="72"/>
+      <c r="AM60" s="73"/>
+    </row>
+    <row r="61" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A61" s="41" t="s">
         <v>935</v>
       </c>
@@ -15924,13 +16221,16 @@
       <c r="AE61" s="56">
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="AF61" s="41"/>
-      <c r="AG61" s="41"/>
-      <c r="AH61" s="41"/>
-      <c r="AI61" s="41"/>
-      <c r="AJ61" s="41"/>
-    </row>
-    <row r="62" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF61" s="72"/>
+      <c r="AG61" s="72"/>
+      <c r="AH61" s="72"/>
+      <c r="AI61" s="72"/>
+      <c r="AJ61" s="72"/>
+      <c r="AK61" s="72"/>
+      <c r="AL61" s="72"/>
+      <c r="AM61" s="73"/>
+    </row>
+    <row r="62" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A62" s="41" t="s">
         <v>935</v>
       </c>
@@ -16028,13 +16328,16 @@
       <c r="AE62" s="56">
         <v>1.6666666666666666E-3</v>
       </c>
-      <c r="AF62" s="41"/>
-      <c r="AG62" s="41"/>
-      <c r="AH62" s="41"/>
-      <c r="AI62" s="41"/>
-      <c r="AJ62" s="41"/>
-    </row>
-    <row r="63" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF62" s="72"/>
+      <c r="AG62" s="72"/>
+      <c r="AH62" s="72"/>
+      <c r="AI62" s="72"/>
+      <c r="AJ62" s="72"/>
+      <c r="AK62" s="72"/>
+      <c r="AL62" s="72"/>
+      <c r="AM62" s="73"/>
+    </row>
+    <row r="63" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A63" s="41" t="s">
         <v>935</v>
       </c>
@@ -16129,13 +16432,16 @@
       <c r="AE63" s="56">
         <v>9.895833333333332E-4</v>
       </c>
-      <c r="AF63" s="41"/>
-      <c r="AG63" s="41"/>
-      <c r="AH63" s="41"/>
-      <c r="AI63" s="41"/>
-      <c r="AJ63" s="41"/>
-    </row>
-    <row r="64" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF63" s="72"/>
+      <c r="AG63" s="72"/>
+      <c r="AH63" s="72"/>
+      <c r="AI63" s="72"/>
+      <c r="AJ63" s="72"/>
+      <c r="AK63" s="72"/>
+      <c r="AL63" s="72"/>
+      <c r="AM63" s="73"/>
+    </row>
+    <row r="64" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A64" s="41" t="s">
         <v>935</v>
       </c>
@@ -16233,13 +16539,16 @@
       <c r="AE64" s="56">
         <v>1.8229166666666667E-3</v>
       </c>
-      <c r="AF64" s="41"/>
-      <c r="AG64" s="41"/>
-      <c r="AH64" s="41"/>
-      <c r="AI64" s="41"/>
-      <c r="AJ64" s="41"/>
-    </row>
-    <row r="65" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF64" s="72"/>
+      <c r="AG64" s="72"/>
+      <c r="AH64" s="72"/>
+      <c r="AI64" s="72"/>
+      <c r="AJ64" s="72"/>
+      <c r="AK64" s="72"/>
+      <c r="AL64" s="72"/>
+      <c r="AM64" s="73"/>
+    </row>
+    <row r="65" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A65" s="41" t="s">
         <v>935</v>
       </c>
@@ -16337,13 +16646,16 @@
       <c r="AE65" s="56">
         <v>1.417824074074074E-3</v>
       </c>
-      <c r="AF65" s="41"/>
-      <c r="AG65" s="41"/>
-      <c r="AH65" s="41"/>
-      <c r="AI65" s="41"/>
-      <c r="AJ65" s="41"/>
-    </row>
-    <row r="66" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF65" s="72"/>
+      <c r="AG65" s="72"/>
+      <c r="AH65" s="72"/>
+      <c r="AI65" s="72"/>
+      <c r="AJ65" s="72"/>
+      <c r="AK65" s="72"/>
+      <c r="AL65" s="72"/>
+      <c r="AM65" s="73"/>
+    </row>
+    <row r="66" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A66" s="41" t="s">
         <v>935</v>
       </c>
@@ -16438,13 +16750,16 @@
       <c r="AE66" s="56">
         <v>1.5624999999999997E-3</v>
       </c>
-      <c r="AF66" s="41"/>
-      <c r="AG66" s="41"/>
-      <c r="AH66" s="41"/>
-      <c r="AI66" s="41"/>
-      <c r="AJ66" s="41"/>
-    </row>
-    <row r="67" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF66" s="72"/>
+      <c r="AG66" s="72"/>
+      <c r="AH66" s="72"/>
+      <c r="AI66" s="72"/>
+      <c r="AJ66" s="72"/>
+      <c r="AK66" s="72"/>
+      <c r="AL66" s="72"/>
+      <c r="AM66" s="73"/>
+    </row>
+    <row r="67" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A67" s="41" t="s">
         <v>935</v>
       </c>
@@ -16542,13 +16857,16 @@
       <c r="AE67" s="56">
         <v>1.4756944444444444E-3</v>
       </c>
-      <c r="AF67" s="41"/>
-      <c r="AG67" s="41"/>
-      <c r="AH67" s="41"/>
-      <c r="AI67" s="41"/>
-      <c r="AJ67" s="41"/>
-    </row>
-    <row r="68" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF67" s="72"/>
+      <c r="AG67" s="72"/>
+      <c r="AH67" s="72"/>
+      <c r="AI67" s="72"/>
+      <c r="AJ67" s="72"/>
+      <c r="AK67" s="72"/>
+      <c r="AL67" s="72"/>
+      <c r="AM67" s="73"/>
+    </row>
+    <row r="68" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A68" s="41" t="s">
         <v>935</v>
       </c>
@@ -16643,13 +16961,16 @@
       <c r="AE68" s="56">
         <v>4.947916666666666E-4</v>
       </c>
-      <c r="AF68" s="41"/>
-      <c r="AG68" s="41"/>
-      <c r="AH68" s="41"/>
-      <c r="AI68" s="41"/>
-      <c r="AJ68" s="41"/>
-    </row>
-    <row r="69" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF68" s="72"/>
+      <c r="AG68" s="72"/>
+      <c r="AH68" s="72"/>
+      <c r="AI68" s="72"/>
+      <c r="AJ68" s="72"/>
+      <c r="AK68" s="72"/>
+      <c r="AL68" s="72"/>
+      <c r="AM68" s="73"/>
+    </row>
+    <row r="69" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A69" s="41" t="s">
         <v>935</v>
       </c>
@@ -16744,13 +17065,16 @@
       <c r="AE69" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF69" s="41"/>
-      <c r="AG69" s="41"/>
-      <c r="AH69" s="41"/>
-      <c r="AI69" s="41"/>
-      <c r="AJ69" s="41"/>
-    </row>
-    <row r="70" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF69" s="72"/>
+      <c r="AG69" s="72"/>
+      <c r="AH69" s="72"/>
+      <c r="AI69" s="72"/>
+      <c r="AJ69" s="72"/>
+      <c r="AK69" s="72"/>
+      <c r="AL69" s="72"/>
+      <c r="AM69" s="73"/>
+    </row>
+    <row r="70" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A70" s="41" t="s">
         <v>935</v>
       </c>
@@ -16845,13 +17169,16 @@
       <c r="AE70" s="56">
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="AF70" s="41"/>
-      <c r="AG70" s="41"/>
-      <c r="AH70" s="41"/>
-      <c r="AI70" s="41"/>
-      <c r="AJ70" s="41"/>
-    </row>
-    <row r="71" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF70" s="72"/>
+      <c r="AG70" s="72"/>
+      <c r="AH70" s="72"/>
+      <c r="AI70" s="72"/>
+      <c r="AJ70" s="72"/>
+      <c r="AK70" s="72"/>
+      <c r="AL70" s="72"/>
+      <c r="AM70" s="73"/>
+    </row>
+    <row r="71" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A71" s="41" t="s">
         <v>935</v>
       </c>
@@ -16946,13 +17273,16 @@
       <c r="AE71" s="56">
         <v>1.2094907407407408E-3</v>
       </c>
-      <c r="AF71" s="41"/>
-      <c r="AG71" s="41"/>
-      <c r="AH71" s="41"/>
-      <c r="AI71" s="41"/>
-      <c r="AJ71" s="41"/>
-    </row>
-    <row r="72" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF71" s="72"/>
+      <c r="AG71" s="72"/>
+      <c r="AH71" s="72"/>
+      <c r="AI71" s="72"/>
+      <c r="AJ71" s="72"/>
+      <c r="AK71" s="72"/>
+      <c r="AL71" s="72"/>
+      <c r="AM71" s="73"/>
+    </row>
+    <row r="72" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A72" s="41" t="s">
         <v>935</v>
       </c>
@@ -17047,13 +17377,16 @@
       <c r="AE72" s="56">
         <v>1.0995370370370369E-3</v>
       </c>
-      <c r="AF72" s="41"/>
-      <c r="AG72" s="41"/>
-      <c r="AH72" s="41"/>
-      <c r="AI72" s="41"/>
-      <c r="AJ72" s="41"/>
-    </row>
-    <row r="73" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF72" s="72"/>
+      <c r="AG72" s="72"/>
+      <c r="AH72" s="72"/>
+      <c r="AI72" s="72"/>
+      <c r="AJ72" s="72"/>
+      <c r="AK72" s="72"/>
+      <c r="AL72" s="72"/>
+      <c r="AM72" s="73"/>
+    </row>
+    <row r="73" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A73" s="41" t="s">
         <v>935</v>
       </c>
@@ -17148,13 +17481,16 @@
       <c r="AE73" s="56">
         <v>1.4293981481481482E-3</v>
       </c>
-      <c r="AF73" s="41"/>
-      <c r="AG73" s="41"/>
-      <c r="AH73" s="41"/>
-      <c r="AI73" s="41"/>
-      <c r="AJ73" s="41"/>
-    </row>
-    <row r="74" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF73" s="72"/>
+      <c r="AG73" s="72"/>
+      <c r="AH73" s="72"/>
+      <c r="AI73" s="72"/>
+      <c r="AJ73" s="72"/>
+      <c r="AK73" s="72"/>
+      <c r="AL73" s="72"/>
+      <c r="AM73" s="73"/>
+    </row>
+    <row r="74" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A74" s="41" t="s">
         <v>935</v>
       </c>
@@ -17249,13 +17585,16 @@
       <c r="AE74" s="56">
         <v>1.3194444444444445E-3</v>
       </c>
-      <c r="AF74" s="41"/>
-      <c r="AG74" s="41"/>
-      <c r="AH74" s="41"/>
-      <c r="AI74" s="41"/>
-      <c r="AJ74" s="41"/>
-    </row>
-    <row r="75" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF74" s="72"/>
+      <c r="AG74" s="72"/>
+      <c r="AH74" s="72"/>
+      <c r="AI74" s="72"/>
+      <c r="AJ74" s="72"/>
+      <c r="AK74" s="72"/>
+      <c r="AL74" s="72"/>
+      <c r="AM74" s="73"/>
+    </row>
+    <row r="75" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A75" s="41" t="s">
         <v>935</v>
       </c>
@@ -17350,13 +17689,16 @@
       <c r="AE75" s="56">
         <v>1.0995370370370369E-3</v>
       </c>
-      <c r="AF75" s="41"/>
-      <c r="AG75" s="41"/>
-      <c r="AH75" s="41"/>
-      <c r="AI75" s="41"/>
-      <c r="AJ75" s="41"/>
-    </row>
-    <row r="76" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF75" s="72"/>
+      <c r="AG75" s="72"/>
+      <c r="AH75" s="72"/>
+      <c r="AI75" s="72"/>
+      <c r="AJ75" s="72"/>
+      <c r="AK75" s="72"/>
+      <c r="AL75" s="72"/>
+      <c r="AM75" s="73"/>
+    </row>
+    <row r="76" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A76" s="41" t="s">
         <v>935</v>
       </c>
@@ -17451,13 +17793,16 @@
       <c r="AE76" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF76" s="41"/>
-      <c r="AG76" s="41"/>
-      <c r="AH76" s="41"/>
-      <c r="AI76" s="41"/>
-      <c r="AJ76" s="41"/>
-    </row>
-    <row r="77" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF76" s="72"/>
+      <c r="AG76" s="72"/>
+      <c r="AH76" s="72"/>
+      <c r="AI76" s="72"/>
+      <c r="AJ76" s="72"/>
+      <c r="AK76" s="72"/>
+      <c r="AL76" s="72"/>
+      <c r="AM76" s="73"/>
+    </row>
+    <row r="77" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A77" s="41" t="s">
         <v>935</v>
       </c>
@@ -17552,13 +17897,16 @@
       <c r="AE77" s="56">
         <v>1.4583333333333332E-3</v>
       </c>
-      <c r="AF77" s="41"/>
-      <c r="AG77" s="41"/>
-      <c r="AH77" s="41"/>
-      <c r="AI77" s="41"/>
-      <c r="AJ77" s="41"/>
-    </row>
-    <row r="78" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF77" s="72"/>
+      <c r="AG77" s="72"/>
+      <c r="AH77" s="72"/>
+      <c r="AI77" s="72"/>
+      <c r="AJ77" s="72"/>
+      <c r="AK77" s="72"/>
+      <c r="AL77" s="72"/>
+      <c r="AM77" s="73"/>
+    </row>
+    <row r="78" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A78" s="41" t="s">
         <v>935</v>
       </c>
@@ -17656,13 +18004,16 @@
       <c r="AE78" s="56">
         <v>1.8749999999999997E-3</v>
       </c>
-      <c r="AF78" s="41"/>
-      <c r="AG78" s="41"/>
-      <c r="AH78" s="41"/>
-      <c r="AI78" s="41"/>
-      <c r="AJ78" s="41"/>
-    </row>
-    <row r="79" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF78" s="72"/>
+      <c r="AG78" s="72"/>
+      <c r="AH78" s="72"/>
+      <c r="AI78" s="72"/>
+      <c r="AJ78" s="72"/>
+      <c r="AK78" s="72"/>
+      <c r="AL78" s="72"/>
+      <c r="AM78" s="73"/>
+    </row>
+    <row r="79" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A79" s="41" t="s">
         <v>935</v>
       </c>
@@ -17760,13 +18111,16 @@
       <c r="AE79" s="56">
         <v>2.0254629629629629E-3</v>
       </c>
-      <c r="AF79" s="41"/>
-      <c r="AG79" s="41"/>
-      <c r="AH79" s="41"/>
-      <c r="AI79" s="41"/>
-      <c r="AJ79" s="41"/>
-    </row>
-    <row r="80" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF79" s="72"/>
+      <c r="AG79" s="72"/>
+      <c r="AH79" s="72"/>
+      <c r="AI79" s="72"/>
+      <c r="AJ79" s="72"/>
+      <c r="AK79" s="72"/>
+      <c r="AL79" s="72"/>
+      <c r="AM79" s="73"/>
+    </row>
+    <row r="80" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A80" s="41" t="s">
         <v>935</v>
       </c>
@@ -17864,13 +18218,16 @@
       <c r="AE80" s="56">
         <v>1.8692129629629629E-3</v>
       </c>
-      <c r="AF80" s="41"/>
-      <c r="AG80" s="41"/>
-      <c r="AH80" s="41"/>
-      <c r="AI80" s="41"/>
-      <c r="AJ80" s="41"/>
-    </row>
-    <row r="81" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF80" s="72"/>
+      <c r="AG80" s="72"/>
+      <c r="AH80" s="72"/>
+      <c r="AI80" s="72"/>
+      <c r="AJ80" s="72"/>
+      <c r="AK80" s="72"/>
+      <c r="AL80" s="72"/>
+      <c r="AM80" s="73"/>
+    </row>
+    <row r="81" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A81" s="41" t="s">
         <v>935</v>
       </c>
@@ -17965,13 +18322,16 @@
       <c r="AE81" s="56">
         <v>7.6967592592592582E-4</v>
       </c>
-      <c r="AF81" s="41"/>
-      <c r="AG81" s="41"/>
-      <c r="AH81" s="41"/>
-      <c r="AI81" s="41"/>
-      <c r="AJ81" s="41"/>
-    </row>
-    <row r="82" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF81" s="72"/>
+      <c r="AG81" s="72"/>
+      <c r="AH81" s="72"/>
+      <c r="AI81" s="72"/>
+      <c r="AJ81" s="72"/>
+      <c r="AK81" s="72"/>
+      <c r="AL81" s="72"/>
+      <c r="AM81" s="73"/>
+    </row>
+    <row r="82" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A82" s="41" t="s">
         <v>935</v>
       </c>
@@ -18069,13 +18429,16 @@
       <c r="AE82" s="56">
         <v>8.564814814814815E-4</v>
       </c>
-      <c r="AF82" s="41"/>
-      <c r="AG82" s="41"/>
-      <c r="AH82" s="41"/>
-      <c r="AI82" s="41"/>
-      <c r="AJ82" s="41"/>
-    </row>
-    <row r="83" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF82" s="72"/>
+      <c r="AG82" s="72"/>
+      <c r="AH82" s="72"/>
+      <c r="AI82" s="72"/>
+      <c r="AJ82" s="72"/>
+      <c r="AK82" s="72"/>
+      <c r="AL82" s="72"/>
+      <c r="AM82" s="73"/>
+    </row>
+    <row r="83" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A83" s="41" t="s">
         <v>935</v>
       </c>
@@ -18173,13 +18536,16 @@
       <c r="AE83" s="56">
         <v>9.3749999999999986E-4</v>
       </c>
-      <c r="AF83" s="41"/>
-      <c r="AG83" s="41"/>
-      <c r="AH83" s="41"/>
-      <c r="AI83" s="41"/>
-      <c r="AJ83" s="41"/>
-    </row>
-    <row r="84" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF83" s="72"/>
+      <c r="AG83" s="72"/>
+      <c r="AH83" s="72"/>
+      <c r="AI83" s="72"/>
+      <c r="AJ83" s="72"/>
+      <c r="AK83" s="72"/>
+      <c r="AL83" s="72"/>
+      <c r="AM83" s="73"/>
+    </row>
+    <row r="84" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A84" s="41" t="s">
         <v>935</v>
       </c>
@@ -18277,13 +18643,16 @@
       <c r="AE84" s="56">
         <v>1.0127314814814814E-3</v>
       </c>
-      <c r="AF84" s="41"/>
-      <c r="AG84" s="41"/>
-      <c r="AH84" s="41"/>
-      <c r="AI84" s="41"/>
-      <c r="AJ84" s="41"/>
-    </row>
-    <row r="85" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF84" s="72"/>
+      <c r="AG84" s="72"/>
+      <c r="AH84" s="72"/>
+      <c r="AI84" s="72"/>
+      <c r="AJ84" s="72"/>
+      <c r="AK84" s="72"/>
+      <c r="AL84" s="72"/>
+      <c r="AM84" s="73"/>
+    </row>
+    <row r="85" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A85" s="41" t="s">
         <v>935</v>
       </c>
@@ -18381,13 +18750,16 @@
       <c r="AE85" s="56">
         <v>7.2916666666666659E-4</v>
       </c>
-      <c r="AF85" s="41"/>
-      <c r="AG85" s="41"/>
-      <c r="AH85" s="41"/>
-      <c r="AI85" s="41"/>
-      <c r="AJ85" s="41"/>
-    </row>
-    <row r="86" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF85" s="72"/>
+      <c r="AG85" s="72"/>
+      <c r="AH85" s="72"/>
+      <c r="AI85" s="72"/>
+      <c r="AJ85" s="72"/>
+      <c r="AK85" s="72"/>
+      <c r="AL85" s="72"/>
+      <c r="AM85" s="73"/>
+    </row>
+    <row r="86" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A86" s="41" t="s">
         <v>935</v>
       </c>
@@ -18485,13 +18857,16 @@
       <c r="AE86" s="56">
         <v>9.1145833333333335E-4</v>
       </c>
-      <c r="AF86" s="41"/>
-      <c r="AG86" s="41"/>
-      <c r="AH86" s="41"/>
-      <c r="AI86" s="41"/>
-      <c r="AJ86" s="41"/>
-    </row>
-    <row r="87" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF86" s="72"/>
+      <c r="AG86" s="72"/>
+      <c r="AH86" s="72"/>
+      <c r="AI86" s="72"/>
+      <c r="AJ86" s="72"/>
+      <c r="AK86" s="72"/>
+      <c r="AL86" s="72"/>
+      <c r="AM86" s="73"/>
+    </row>
+    <row r="87" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A87" s="41" t="s">
         <v>935</v>
       </c>
@@ -18589,13 +18964,16 @@
       <c r="AE87" s="56">
         <v>8.1018518518518527E-4</v>
       </c>
-      <c r="AF87" s="41"/>
-      <c r="AG87" s="41"/>
-      <c r="AH87" s="41"/>
-      <c r="AI87" s="41"/>
-      <c r="AJ87" s="41"/>
-    </row>
-    <row r="88" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF87" s="72"/>
+      <c r="AG87" s="72"/>
+      <c r="AH87" s="72"/>
+      <c r="AI87" s="72"/>
+      <c r="AJ87" s="72"/>
+      <c r="AK87" s="72"/>
+      <c r="AL87" s="72"/>
+      <c r="AM87" s="73"/>
+    </row>
+    <row r="88" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A88" s="41" t="s">
         <v>935</v>
       </c>
@@ -18693,13 +19071,16 @@
       <c r="AE88" s="56">
         <v>2.5578703703703705E-3</v>
       </c>
-      <c r="AF88" s="41"/>
-      <c r="AG88" s="41"/>
-      <c r="AH88" s="41"/>
-      <c r="AI88" s="41"/>
-      <c r="AJ88" s="41"/>
-    </row>
-    <row r="89" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF88" s="72"/>
+      <c r="AG88" s="72"/>
+      <c r="AH88" s="72"/>
+      <c r="AI88" s="72"/>
+      <c r="AJ88" s="72"/>
+      <c r="AK88" s="72"/>
+      <c r="AL88" s="72"/>
+      <c r="AM88" s="73"/>
+    </row>
+    <row r="89" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A89" s="41" t="s">
         <v>935</v>
       </c>
@@ -18797,13 +19178,16 @@
       <c r="AE89" s="56">
         <v>6.4236111111111113E-4</v>
       </c>
-      <c r="AF89" s="41"/>
-      <c r="AG89" s="41"/>
-      <c r="AH89" s="41"/>
-      <c r="AI89" s="41"/>
-      <c r="AJ89" s="41"/>
-    </row>
-    <row r="90" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF89" s="72"/>
+      <c r="AG89" s="72"/>
+      <c r="AH89" s="72"/>
+      <c r="AI89" s="72"/>
+      <c r="AJ89" s="72"/>
+      <c r="AK89" s="72"/>
+      <c r="AL89" s="72"/>
+      <c r="AM89" s="73"/>
+    </row>
+    <row r="90" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A90" s="41" t="s">
         <v>935</v>
       </c>
@@ -18898,13 +19282,16 @@
       <c r="AE90" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF90" s="41"/>
-      <c r="AG90" s="41"/>
-      <c r="AH90" s="41"/>
-      <c r="AI90" s="41"/>
-      <c r="AJ90" s="41"/>
-    </row>
-    <row r="91" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF90" s="72"/>
+      <c r="AG90" s="72"/>
+      <c r="AH90" s="72"/>
+      <c r="AI90" s="72"/>
+      <c r="AJ90" s="72"/>
+      <c r="AK90" s="72"/>
+      <c r="AL90" s="72"/>
+      <c r="AM90" s="73"/>
+    </row>
+    <row r="91" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A91" s="41" t="s">
         <v>935</v>
       </c>
@@ -19002,13 +19389,16 @@
       <c r="AE91" s="56">
         <v>5.4976851851851844E-4</v>
       </c>
-      <c r="AF91" s="41"/>
-      <c r="AG91" s="41"/>
-      <c r="AH91" s="41"/>
-      <c r="AI91" s="41"/>
-      <c r="AJ91" s="41"/>
-    </row>
-    <row r="92" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF91" s="72"/>
+      <c r="AG91" s="72"/>
+      <c r="AH91" s="72"/>
+      <c r="AI91" s="72"/>
+      <c r="AJ91" s="72"/>
+      <c r="AK91" s="72"/>
+      <c r="AL91" s="72"/>
+      <c r="AM91" s="73"/>
+    </row>
+    <row r="92" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A92" s="41" t="s">
         <v>935</v>
       </c>
@@ -19106,13 +19496,16 @@
       <c r="AE92" s="56">
         <v>8.3333333333333328E-4</v>
       </c>
-      <c r="AF92" s="41"/>
-      <c r="AG92" s="41"/>
-      <c r="AH92" s="41"/>
-      <c r="AI92" s="41"/>
-      <c r="AJ92" s="41"/>
-    </row>
-    <row r="93" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF92" s="72"/>
+      <c r="AG92" s="72"/>
+      <c r="AH92" s="72"/>
+      <c r="AI92" s="72"/>
+      <c r="AJ92" s="72"/>
+      <c r="AK92" s="72"/>
+      <c r="AL92" s="72"/>
+      <c r="AM92" s="73"/>
+    </row>
+    <row r="93" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A93" s="41" t="s">
         <v>935</v>
       </c>
@@ -19210,13 +19603,16 @@
       <c r="AE93" s="56">
         <v>8.8541666666666662E-4</v>
       </c>
-      <c r="AF93" s="41"/>
-      <c r="AG93" s="41"/>
-      <c r="AH93" s="41"/>
-      <c r="AI93" s="41"/>
-      <c r="AJ93" s="41"/>
-    </row>
-    <row r="94" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF93" s="72"/>
+      <c r="AG93" s="72"/>
+      <c r="AH93" s="72"/>
+      <c r="AI93" s="72"/>
+      <c r="AJ93" s="72"/>
+      <c r="AK93" s="72"/>
+      <c r="AL93" s="72"/>
+      <c r="AM93" s="73"/>
+    </row>
+    <row r="94" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A94" s="41" t="s">
         <v>935</v>
       </c>
@@ -19316,13 +19712,22 @@
       <c r="AE94" s="56">
         <v>3.4432870370370368E-4</v>
       </c>
-      <c r="AF94" s="41"/>
-      <c r="AG94" s="41"/>
-      <c r="AH94" s="41"/>
-      <c r="AI94" s="41"/>
-      <c r="AJ94" s="41"/>
-    </row>
-    <row r="95" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF94" s="72" t="str">
+        <f t="shared" ref="AF94:AF142" si="13">""</f>
+        <v/>
+      </c>
+      <c r="AG94" s="72"/>
+      <c r="AH94" s="72" t="str">
+        <f t="shared" ref="AH94:AH142" si="14">""</f>
+        <v/>
+      </c>
+      <c r="AI94" s="72"/>
+      <c r="AJ94" s="72"/>
+      <c r="AK94" s="72"/>
+      <c r="AL94" s="72"/>
+      <c r="AM94" s="73"/>
+    </row>
+    <row r="95" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A95" s="41" t="s">
         <v>935</v>
       </c>
@@ -19420,13 +19825,16 @@
       <c r="AE95" s="56">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="AF95" s="41"/>
-      <c r="AG95" s="41"/>
-      <c r="AH95" s="41"/>
-      <c r="AI95" s="41"/>
-      <c r="AJ95" s="41"/>
-    </row>
-    <row r="96" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF95" s="72"/>
+      <c r="AG95" s="72"/>
+      <c r="AH95" s="72"/>
+      <c r="AI95" s="72"/>
+      <c r="AJ95" s="72"/>
+      <c r="AK95" s="72"/>
+      <c r="AL95" s="72"/>
+      <c r="AM95" s="73"/>
+    </row>
+    <row r="96" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A96" s="41" t="s">
         <v>935</v>
       </c>
@@ -19524,13 +19932,24 @@
       <c r="AE96" s="56">
         <v>8.8541666666666662E-4</v>
       </c>
-      <c r="AF96" s="41"/>
-      <c r="AG96" s="41"/>
-      <c r="AH96" s="41"/>
-      <c r="AI96" s="41"/>
-      <c r="AJ96" s="41"/>
-    </row>
-    <row r="97" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF96" s="74">
+        <v>750</v>
+      </c>
+      <c r="AG96" s="74">
+        <v>3</v>
+      </c>
+      <c r="AH96" s="74">
+        <v>210</v>
+      </c>
+      <c r="AI96" s="74">
+        <v>120</v>
+      </c>
+      <c r="AJ96" s="74"/>
+      <c r="AK96" s="74"/>
+      <c r="AL96" s="74"/>
+      <c r="AM96" s="73"/>
+    </row>
+    <row r="97" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A97" s="41" t="s">
         <v>935</v>
       </c>
@@ -19630,13 +20049,22 @@
       <c r="AE97" s="56">
         <v>4.7743055555555549E-4</v>
       </c>
-      <c r="AF97" s="41"/>
-      <c r="AG97" s="41"/>
-      <c r="AH97" s="41"/>
-      <c r="AI97" s="41"/>
-      <c r="AJ97" s="41"/>
-    </row>
-    <row r="98" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF97" s="72" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG97" s="72"/>
+      <c r="AH97" s="72" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI97" s="72"/>
+      <c r="AJ97" s="72"/>
+      <c r="AK97" s="72"/>
+      <c r="AL97" s="72"/>
+      <c r="AM97" s="73"/>
+    </row>
+    <row r="98" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A98" s="41" t="s">
         <v>935</v>
       </c>
@@ -19731,13 +20159,16 @@
       <c r="AE98" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF98" s="41"/>
-      <c r="AG98" s="41"/>
-      <c r="AH98" s="41"/>
-      <c r="AI98" s="41"/>
-      <c r="AJ98" s="41"/>
-    </row>
-    <row r="99" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF98" s="72"/>
+      <c r="AG98" s="72"/>
+      <c r="AH98" s="72"/>
+      <c r="AI98" s="72"/>
+      <c r="AJ98" s="72"/>
+      <c r="AK98" s="72"/>
+      <c r="AL98" s="72"/>
+      <c r="AM98" s="73"/>
+    </row>
+    <row r="99" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A99" s="41" t="s">
         <v>935</v>
       </c>
@@ -19835,13 +20266,16 @@
       <c r="AE99" s="56">
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="AF99" s="41"/>
-      <c r="AG99" s="41"/>
-      <c r="AH99" s="41"/>
-      <c r="AI99" s="41"/>
-      <c r="AJ99" s="41"/>
-    </row>
-    <row r="100" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF99" s="72"/>
+      <c r="AG99" s="72"/>
+      <c r="AH99" s="72"/>
+      <c r="AI99" s="72"/>
+      <c r="AJ99" s="72"/>
+      <c r="AK99" s="72"/>
+      <c r="AL99" s="72"/>
+      <c r="AM99" s="73"/>
+    </row>
+    <row r="100" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A100" s="41" t="s">
         <v>991</v>
       </c>
@@ -19936,13 +20370,16 @@
       <c r="AE100" s="56">
         <v>1.0995370370370369E-3</v>
       </c>
-      <c r="AF100" s="41"/>
-      <c r="AG100" s="41"/>
-      <c r="AH100" s="41"/>
-      <c r="AI100" s="41"/>
-      <c r="AJ100" s="41"/>
-    </row>
-    <row r="101" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF100" s="72"/>
+      <c r="AG100" s="72"/>
+      <c r="AH100" s="72"/>
+      <c r="AI100" s="72"/>
+      <c r="AJ100" s="72"/>
+      <c r="AK100" s="72"/>
+      <c r="AL100" s="72"/>
+      <c r="AM100" s="73"/>
+    </row>
+    <row r="101" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A101" s="41" t="s">
         <v>991</v>
       </c>
@@ -20040,13 +20477,16 @@
       <c r="AE101" s="56">
         <v>1.0995370370370369E-3</v>
       </c>
-      <c r="AF101" s="41"/>
-      <c r="AG101" s="41"/>
-      <c r="AH101" s="41"/>
-      <c r="AI101" s="41"/>
-      <c r="AJ101" s="41"/>
-    </row>
-    <row r="102" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF101" s="72"/>
+      <c r="AG101" s="72"/>
+      <c r="AH101" s="72"/>
+      <c r="AI101" s="72"/>
+      <c r="AJ101" s="72"/>
+      <c r="AK101" s="72"/>
+      <c r="AL101" s="72"/>
+      <c r="AM101" s="73"/>
+    </row>
+    <row r="102" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A102" s="41" t="s">
         <v>991</v>
       </c>
@@ -20087,7 +20527,7 @@
         <v>408</v>
       </c>
       <c r="N102" s="54">
-        <f t="shared" ref="N102:N123" si="13">N101+(IFERROR(VALUE(LEFT(L102,FIND("분",L102)-1))*60,0)+IFERROR(VALUE(TRIM(MID(L102,IFERROR(FIND("분",L102),0)+1,IFERROR(FIND("초",L102),LEN(L102)+1)-IFERROR(FIND("분",L102),0)-1))),0))/86400</f>
+        <f t="shared" ref="N102:N123" si="15">N101+(IFERROR(VALUE(LEFT(L102,FIND("분",L102)-1))*60,0)+IFERROR(VALUE(TRIM(MID(L102,IFERROR(FIND("분",L102),0)+1,IFERROR(FIND("초",L102),LEN(L102)+1)-IFERROR(FIND("분",L102),0)-1))),0))/86400</f>
         <v>0.1115740740740741</v>
       </c>
       <c r="O102" s="41" t="s">
@@ -20141,13 +20581,16 @@
       <c r="AE102" s="56">
         <v>1.3194444444444445E-3</v>
       </c>
-      <c r="AF102" s="41"/>
-      <c r="AG102" s="41"/>
-      <c r="AH102" s="41"/>
-      <c r="AI102" s="41"/>
-      <c r="AJ102" s="41"/>
-    </row>
-    <row r="103" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF102" s="72"/>
+      <c r="AG102" s="72"/>
+      <c r="AH102" s="72"/>
+      <c r="AI102" s="72"/>
+      <c r="AJ102" s="72"/>
+      <c r="AK102" s="72"/>
+      <c r="AL102" s="72"/>
+      <c r="AM102" s="73"/>
+    </row>
+    <row r="103" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A103" s="41" t="s">
         <v>991</v>
       </c>
@@ -20188,7 +20631,7 @@
         <v>395</v>
       </c>
       <c r="N103" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.11307870370370374</v>
       </c>
       <c r="O103" s="41" t="s">
@@ -20242,13 +20685,16 @@
       <c r="AE103" s="56">
         <v>1.3917824074074073E-3</v>
       </c>
-      <c r="AF103" s="41"/>
-      <c r="AG103" s="41"/>
-      <c r="AH103" s="41"/>
-      <c r="AI103" s="41"/>
-      <c r="AJ103" s="41"/>
-    </row>
-    <row r="104" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF103" s="72"/>
+      <c r="AG103" s="72"/>
+      <c r="AH103" s="72"/>
+      <c r="AI103" s="72"/>
+      <c r="AJ103" s="72"/>
+      <c r="AK103" s="72"/>
+      <c r="AL103" s="72"/>
+      <c r="AM103" s="73"/>
+    </row>
+    <row r="104" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A104" s="41" t="s">
         <v>991</v>
       </c>
@@ -20289,7 +20735,7 @@
         <v>577</v>
       </c>
       <c r="N104" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.11481481481481484</v>
       </c>
       <c r="O104" s="41" t="s">
@@ -20323,15 +20769,15 @@
         <v>60</v>
       </c>
       <c r="Y104" s="43">
-        <f t="shared" ref="Y104:Y109" si="14">IF(ISNUMBER(X104),ROUND(X104*0.85,0),"—")</f>
+        <f t="shared" ref="Y104:Y109" si="16">IF(ISNUMBER(X104),ROUND(X104*0.85,0),"—")</f>
         <v>51</v>
       </c>
       <c r="Z104" s="43">
-        <f t="shared" ref="Z104:Z109" si="15">IF(ISNUMBER(X104),ROUND(X104*0.7,0),"—")</f>
+        <f t="shared" ref="Z104:Z109" si="17">IF(ISNUMBER(X104),ROUND(X104*0.7,0),"—")</f>
         <v>42</v>
       </c>
       <c r="AA104" s="43">
-        <f t="shared" ref="AA104:AA109" si="16">IF(ISNUMBER(X104),ROUND(X104*0.55,0),"—")</f>
+        <f t="shared" ref="AA104:AA109" si="18">IF(ISNUMBER(X104),ROUND(X104*0.55,0),"—")</f>
         <v>33</v>
       </c>
       <c r="AB104" s="56">
@@ -20346,13 +20792,24 @@
       <c r="AE104" s="56">
         <v>1.6059027777777775E-3</v>
       </c>
-      <c r="AF104" s="41"/>
-      <c r="AG104" s="41"/>
-      <c r="AH104" s="41"/>
-      <c r="AI104" s="41"/>
-      <c r="AJ104" s="41"/>
-    </row>
-    <row r="105" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF104" s="74">
+        <v>900</v>
+      </c>
+      <c r="AG104" s="74">
+        <v>3</v>
+      </c>
+      <c r="AH104" s="74">
+        <v>210</v>
+      </c>
+      <c r="AI104" s="74">
+        <v>210</v>
+      </c>
+      <c r="AJ104" s="74"/>
+      <c r="AK104" s="74"/>
+      <c r="AL104" s="74"/>
+      <c r="AM104" s="73"/>
+    </row>
+    <row r="105" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A105" s="41" t="s">
         <v>991</v>
       </c>
@@ -20393,7 +20850,7 @@
         <v>185</v>
       </c>
       <c r="N105" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.11620370370370373</v>
       </c>
       <c r="O105" s="41" t="s">
@@ -20427,15 +20884,15 @@
         <v>60</v>
       </c>
       <c r="Y105" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>51</v>
       </c>
       <c r="Z105" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AA105" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="AB105" s="56">
@@ -20450,13 +20907,16 @@
       <c r="AE105" s="56">
         <v>1.2152777777777778E-3</v>
       </c>
-      <c r="AF105" s="41"/>
-      <c r="AG105" s="41"/>
-      <c r="AH105" s="41"/>
-      <c r="AI105" s="41"/>
-      <c r="AJ105" s="41"/>
-    </row>
-    <row r="106" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF105" s="72"/>
+      <c r="AG105" s="72"/>
+      <c r="AH105" s="72"/>
+      <c r="AI105" s="72"/>
+      <c r="AJ105" s="72"/>
+      <c r="AK105" s="72"/>
+      <c r="AL105" s="72"/>
+      <c r="AM105" s="73"/>
+    </row>
+    <row r="106" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A106" s="41" t="s">
         <v>991</v>
       </c>
@@ -20497,7 +20957,7 @@
         <v>670</v>
       </c>
       <c r="N106" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.11863425925925929</v>
       </c>
       <c r="O106" s="41" t="s">
@@ -20531,15 +20991,15 @@
         <v>30</v>
       </c>
       <c r="Y106" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>26</v>
       </c>
       <c r="Z106" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="AA106" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>17</v>
       </c>
       <c r="AB106" s="56">
@@ -20554,13 +21014,16 @@
       <c r="AE106" s="56">
         <v>2.1874999999999998E-3</v>
       </c>
-      <c r="AF106" s="41"/>
-      <c r="AG106" s="41"/>
-      <c r="AH106" s="41"/>
-      <c r="AI106" s="41"/>
-      <c r="AJ106" s="41"/>
-    </row>
-    <row r="107" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF106" s="72"/>
+      <c r="AG106" s="72"/>
+      <c r="AH106" s="72"/>
+      <c r="AI106" s="72"/>
+      <c r="AJ106" s="72"/>
+      <c r="AK106" s="72"/>
+      <c r="AL106" s="72"/>
+      <c r="AM106" s="73"/>
+    </row>
+    <row r="107" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A107" s="41" t="s">
         <v>991</v>
       </c>
@@ -20601,7 +21064,7 @@
         <v>593</v>
       </c>
       <c r="N107" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12071759259259263</v>
       </c>
       <c r="O107" s="41" t="s">
@@ -20635,15 +21098,15 @@
         <v>60</v>
       </c>
       <c r="Y107" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>51</v>
       </c>
       <c r="Z107" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AA107" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="AB107" s="56">
@@ -20658,13 +21121,16 @@
       <c r="AE107" s="56">
         <v>1.7708333333333332E-3</v>
       </c>
-      <c r="AF107" s="41"/>
-      <c r="AG107" s="41"/>
-      <c r="AH107" s="41"/>
-      <c r="AI107" s="41"/>
-      <c r="AJ107" s="41"/>
-    </row>
-    <row r="108" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF107" s="72"/>
+      <c r="AG107" s="72"/>
+      <c r="AH107" s="72"/>
+      <c r="AI107" s="72"/>
+      <c r="AJ107" s="72"/>
+      <c r="AK107" s="72"/>
+      <c r="AL107" s="72"/>
+      <c r="AM107" s="73"/>
+    </row>
+    <row r="108" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A108" s="41" t="s">
         <v>991</v>
       </c>
@@ -20705,7 +21171,7 @@
         <v>411</v>
       </c>
       <c r="N108" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12303240740740744</v>
       </c>
       <c r="O108" s="41" t="s">
@@ -20739,15 +21205,15 @@
         <v>30</v>
       </c>
       <c r="Y108" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>26</v>
       </c>
       <c r="Z108" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="AA108" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>17</v>
       </c>
       <c r="AB108" s="56">
@@ -20762,13 +21228,16 @@
       <c r="AE108" s="56">
         <v>2.1412037037037033E-3</v>
       </c>
-      <c r="AF108" s="41"/>
-      <c r="AG108" s="41"/>
-      <c r="AH108" s="41"/>
-      <c r="AI108" s="41"/>
-      <c r="AJ108" s="41"/>
-    </row>
-    <row r="109" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF108" s="72"/>
+      <c r="AG108" s="72"/>
+      <c r="AH108" s="72"/>
+      <c r="AI108" s="72"/>
+      <c r="AJ108" s="72"/>
+      <c r="AK108" s="72"/>
+      <c r="AL108" s="72"/>
+      <c r="AM108" s="73"/>
+    </row>
+    <row r="109" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A109" s="41" t="s">
         <v>991</v>
       </c>
@@ -20809,7 +21278,7 @@
         <v>696</v>
       </c>
       <c r="N109" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12534722222222225</v>
       </c>
       <c r="O109" s="41" t="s">
@@ -20843,15 +21312,15 @@
         <v>60</v>
       </c>
       <c r="Y109" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>51</v>
       </c>
       <c r="Z109" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AA109" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="AB109" s="56">
@@ -20866,13 +21335,16 @@
       <c r="AE109" s="56">
         <v>2.0254629629629629E-3</v>
       </c>
-      <c r="AF109" s="41"/>
-      <c r="AG109" s="41"/>
-      <c r="AH109" s="41"/>
-      <c r="AI109" s="41"/>
-      <c r="AJ109" s="41"/>
-    </row>
-    <row r="110" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF109" s="72"/>
+      <c r="AG109" s="72"/>
+      <c r="AH109" s="72"/>
+      <c r="AI109" s="72"/>
+      <c r="AJ109" s="72"/>
+      <c r="AK109" s="72"/>
+      <c r="AL109" s="72"/>
+      <c r="AM109" s="73"/>
+    </row>
+    <row r="110" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A110" s="41" t="s">
         <v>991</v>
       </c>
@@ -20913,7 +21385,7 @@
         <v>384</v>
       </c>
       <c r="N110" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12650462962962966</v>
       </c>
       <c r="O110" s="41" t="s">
@@ -20967,13 +21439,16 @@
       <c r="AE110" s="56">
         <v>1.0416666666666664E-3</v>
       </c>
-      <c r="AF110" s="41"/>
-      <c r="AG110" s="41"/>
-      <c r="AH110" s="41"/>
-      <c r="AI110" s="41"/>
-      <c r="AJ110" s="41"/>
-    </row>
-    <row r="111" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF110" s="72"/>
+      <c r="AG110" s="72"/>
+      <c r="AH110" s="72"/>
+      <c r="AI110" s="72"/>
+      <c r="AJ110" s="72"/>
+      <c r="AK110" s="72"/>
+      <c r="AL110" s="72"/>
+      <c r="AM110" s="73"/>
+    </row>
+    <row r="111" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A111" s="41" t="s">
         <v>991</v>
       </c>
@@ -21014,7 +21489,7 @@
         <v>797</v>
       </c>
       <c r="N111" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12870370370370374</v>
       </c>
       <c r="O111" s="41" t="s">
@@ -21048,15 +21523,15 @@
         <v>30</v>
       </c>
       <c r="Y111" s="43">
-        <f t="shared" ref="Y111:Y117" si="17">IF(ISNUMBER(X111),ROUND(X111*0.85,0),"—")</f>
+        <f t="shared" ref="Y111:Y117" si="19">IF(ISNUMBER(X111),ROUND(X111*0.85,0),"—")</f>
         <v>26</v>
       </c>
       <c r="Z111" s="43">
-        <f t="shared" ref="Z111:Z117" si="18">IF(ISNUMBER(X111),ROUND(X111*0.7,0),"—")</f>
+        <f t="shared" ref="Z111:Z117" si="20">IF(ISNUMBER(X111),ROUND(X111*0.7,0),"—")</f>
         <v>21</v>
       </c>
       <c r="AA111" s="43">
-        <f t="shared" ref="AA111:AA117" si="19">IF(ISNUMBER(X111),ROUND(X111*0.55,0),"—")</f>
+        <f t="shared" ref="AA111:AA117" si="21">IF(ISNUMBER(X111),ROUND(X111*0.55,0),"—")</f>
         <v>17</v>
       </c>
       <c r="AB111" s="56">
@@ -21071,13 +21546,16 @@
       <c r="AE111" s="56">
         <v>2.0341435185185185E-3</v>
       </c>
-      <c r="AF111" s="41"/>
-      <c r="AG111" s="41"/>
-      <c r="AH111" s="41"/>
-      <c r="AI111" s="41"/>
-      <c r="AJ111" s="41"/>
-    </row>
-    <row r="112" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF111" s="72"/>
+      <c r="AG111" s="72"/>
+      <c r="AH111" s="72"/>
+      <c r="AI111" s="72"/>
+      <c r="AJ111" s="72"/>
+      <c r="AK111" s="72"/>
+      <c r="AL111" s="72"/>
+      <c r="AM111" s="73"/>
+    </row>
+    <row r="112" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A112" s="41" t="s">
         <v>991</v>
       </c>
@@ -21118,7 +21596,7 @@
         <v>125</v>
       </c>
       <c r="N112" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13043981481481484</v>
       </c>
       <c r="O112" s="41" t="s">
@@ -21152,15 +21630,15 @@
         <v>30</v>
       </c>
       <c r="Y112" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>26</v>
       </c>
       <c r="Z112" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="AA112" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="AB112" s="56">
@@ -21175,13 +21653,16 @@
       <c r="AE112" s="56">
         <v>1.519097222222222E-3</v>
       </c>
-      <c r="AF112" s="41"/>
-      <c r="AG112" s="41"/>
-      <c r="AH112" s="41"/>
-      <c r="AI112" s="41"/>
-      <c r="AJ112" s="41"/>
-    </row>
-    <row r="113" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF112" s="72"/>
+      <c r="AG112" s="72"/>
+      <c r="AH112" s="72"/>
+      <c r="AI112" s="72"/>
+      <c r="AJ112" s="72"/>
+      <c r="AK112" s="72"/>
+      <c r="AL112" s="72"/>
+      <c r="AM112" s="73"/>
+    </row>
+    <row r="113" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A113" s="41" t="s">
         <v>991</v>
       </c>
@@ -21222,7 +21703,7 @@
         <v>700</v>
       </c>
       <c r="N113" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13182870370370373</v>
       </c>
       <c r="O113" s="41" t="s">
@@ -21256,15 +21737,15 @@
         <v>50</v>
       </c>
       <c r="Y113" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>43</v>
       </c>
       <c r="Z113" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>35</v>
       </c>
       <c r="AA113" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>28</v>
       </c>
       <c r="AB113" s="56">
@@ -21279,13 +21760,16 @@
       <c r="AE113" s="56">
         <v>1.1805555555555556E-3</v>
       </c>
-      <c r="AF113" s="41"/>
-      <c r="AG113" s="41"/>
-      <c r="AH113" s="41"/>
-      <c r="AI113" s="41"/>
-      <c r="AJ113" s="41"/>
-    </row>
-    <row r="114" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF113" s="72"/>
+      <c r="AG113" s="72"/>
+      <c r="AH113" s="72"/>
+      <c r="AI113" s="72"/>
+      <c r="AJ113" s="72"/>
+      <c r="AK113" s="72"/>
+      <c r="AL113" s="72"/>
+      <c r="AM113" s="73"/>
+    </row>
+    <row r="114" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A114" s="41" t="s">
         <v>991</v>
       </c>
@@ -21326,7 +21810,7 @@
         <v>1021</v>
       </c>
       <c r="N114" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13263888888888892</v>
       </c>
       <c r="O114" s="41" t="s">
@@ -21360,15 +21844,15 @@
         <v>30</v>
       </c>
       <c r="Y114" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>26</v>
       </c>
       <c r="Z114" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="AA114" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="AB114" s="56">
@@ -21383,13 +21867,24 @@
       <c r="AE114" s="56">
         <v>7.4942129629629621E-4</v>
       </c>
-      <c r="AF114" s="41"/>
-      <c r="AG114" s="41"/>
-      <c r="AH114" s="41"/>
-      <c r="AI114" s="41"/>
-      <c r="AJ114" s="41"/>
-    </row>
-    <row r="115" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF114" s="74">
+        <v>1050</v>
+      </c>
+      <c r="AG114" s="74">
+        <v>3</v>
+      </c>
+      <c r="AH114" s="74">
+        <v>120</v>
+      </c>
+      <c r="AI114" s="74">
+        <v>330</v>
+      </c>
+      <c r="AJ114" s="74"/>
+      <c r="AK114" s="74"/>
+      <c r="AL114" s="74"/>
+      <c r="AM114" s="73"/>
+    </row>
+    <row r="115" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A115" s="41" t="s">
         <v>991</v>
       </c>
@@ -21430,7 +21925,7 @@
         <v>192</v>
       </c>
       <c r="N115" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.1330439814814815</v>
       </c>
       <c r="O115" s="41" t="s">
@@ -21464,15 +21959,15 @@
         <v>50</v>
       </c>
       <c r="Y115" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>43</v>
       </c>
       <c r="Z115" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>35</v>
       </c>
       <c r="AA115" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>28</v>
       </c>
       <c r="AB115" s="56">
@@ -21487,13 +21982,22 @@
       <c r="AE115" s="56">
         <v>3.4432870370370368E-4</v>
       </c>
-      <c r="AF115" s="41"/>
-      <c r="AG115" s="41"/>
-      <c r="AH115" s="41"/>
-      <c r="AI115" s="41"/>
-      <c r="AJ115" s="41"/>
-    </row>
-    <row r="116" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF115" s="72" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG115" s="72"/>
+      <c r="AH115" s="72" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI115" s="72"/>
+      <c r="AJ115" s="72"/>
+      <c r="AK115" s="72"/>
+      <c r="AL115" s="72"/>
+      <c r="AM115" s="73"/>
+    </row>
+    <row r="116" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A116" s="41" t="s">
         <v>991</v>
       </c>
@@ -21534,7 +22038,7 @@
         <v>696</v>
       </c>
       <c r="N116" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13582175925925927</v>
       </c>
       <c r="O116" s="41" t="s">
@@ -21568,15 +22072,15 @@
         <v>60</v>
       </c>
       <c r="Y116" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>51</v>
       </c>
       <c r="Z116" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>42</v>
       </c>
       <c r="AA116" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AB116" s="56">
@@ -21591,13 +22095,16 @@
       <c r="AE116" s="56">
         <v>2.3611111111111111E-3</v>
       </c>
-      <c r="AF116" s="41"/>
-      <c r="AG116" s="41"/>
-      <c r="AH116" s="41"/>
-      <c r="AI116" s="41"/>
-      <c r="AJ116" s="41"/>
-    </row>
-    <row r="117" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF116" s="72"/>
+      <c r="AG116" s="72"/>
+      <c r="AH116" s="72"/>
+      <c r="AI116" s="72"/>
+      <c r="AJ116" s="72"/>
+      <c r="AK116" s="72"/>
+      <c r="AL116" s="72"/>
+      <c r="AM116" s="73"/>
+    </row>
+    <row r="117" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A117" s="41" t="s">
         <v>991</v>
       </c>
@@ -21638,7 +22145,7 @@
         <v>664</v>
       </c>
       <c r="N117" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13825231481481481</v>
       </c>
       <c r="O117" s="41" t="s">
@@ -21672,15 +22179,15 @@
         <v>30</v>
       </c>
       <c r="Y117" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>26</v>
       </c>
       <c r="Z117" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="AA117" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="AB117" s="56">
@@ -21695,13 +22202,16 @@
       <c r="AE117" s="56">
         <v>2.1874999999999998E-3</v>
       </c>
-      <c r="AF117" s="41"/>
-      <c r="AG117" s="41"/>
-      <c r="AH117" s="41"/>
-      <c r="AI117" s="41"/>
-      <c r="AJ117" s="41"/>
-    </row>
-    <row r="118" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF117" s="72"/>
+      <c r="AG117" s="72"/>
+      <c r="AH117" s="72"/>
+      <c r="AI117" s="72"/>
+      <c r="AJ117" s="72"/>
+      <c r="AK117" s="72"/>
+      <c r="AL117" s="72"/>
+      <c r="AM117" s="73"/>
+    </row>
+    <row r="118" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A118" s="41" t="s">
         <v>991</v>
       </c>
@@ -21742,7 +22252,7 @@
         <v>384</v>
       </c>
       <c r="N118" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13952546296296298</v>
       </c>
       <c r="O118" s="41" t="s">
@@ -21796,13 +22306,16 @@
       <c r="AE118" s="56">
         <v>1.1458333333333333E-3</v>
       </c>
-      <c r="AF118" s="41"/>
-      <c r="AG118" s="41"/>
-      <c r="AH118" s="41"/>
-      <c r="AI118" s="41"/>
-      <c r="AJ118" s="41"/>
-    </row>
-    <row r="119" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF118" s="72"/>
+      <c r="AG118" s="72"/>
+      <c r="AH118" s="72"/>
+      <c r="AI118" s="72"/>
+      <c r="AJ118" s="72"/>
+      <c r="AK118" s="72"/>
+      <c r="AL118" s="72"/>
+      <c r="AM118" s="73"/>
+    </row>
+    <row r="119" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A119" s="41" t="s">
         <v>991</v>
       </c>
@@ -21843,7 +22356,7 @@
         <v>657</v>
       </c>
       <c r="N119" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.14172453703703705</v>
       </c>
       <c r="O119" s="41" t="s">
@@ -21900,13 +22413,16 @@
       <c r="AE119" s="56">
         <v>1.924189814814815E-3</v>
       </c>
-      <c r="AF119" s="41"/>
-      <c r="AG119" s="41"/>
-      <c r="AH119" s="41"/>
-      <c r="AI119" s="41"/>
-      <c r="AJ119" s="41"/>
-    </row>
-    <row r="120" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF119" s="72"/>
+      <c r="AG119" s="72"/>
+      <c r="AH119" s="72"/>
+      <c r="AI119" s="72"/>
+      <c r="AJ119" s="72"/>
+      <c r="AK119" s="72"/>
+      <c r="AL119" s="72"/>
+      <c r="AM119" s="73"/>
+    </row>
+    <row r="120" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A120" s="41" t="s">
         <v>991</v>
       </c>
@@ -21947,7 +22463,7 @@
         <v>1027</v>
       </c>
       <c r="N120" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.1441550925925926</v>
       </c>
       <c r="O120" s="41" t="s">
@@ -22004,13 +22520,16 @@
       <c r="AE120" s="56">
         <v>2.1874999999999998E-3</v>
       </c>
-      <c r="AF120" s="41"/>
-      <c r="AG120" s="41"/>
-      <c r="AH120" s="41"/>
-      <c r="AI120" s="41"/>
-      <c r="AJ120" s="41"/>
-    </row>
-    <row r="121" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF120" s="72"/>
+      <c r="AG120" s="72"/>
+      <c r="AH120" s="72"/>
+      <c r="AI120" s="72"/>
+      <c r="AJ120" s="72"/>
+      <c r="AK120" s="72"/>
+      <c r="AL120" s="72"/>
+      <c r="AM120" s="73"/>
+    </row>
+    <row r="121" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A121" s="41" t="s">
         <v>991</v>
       </c>
@@ -22051,7 +22570,7 @@
         <v>577</v>
       </c>
       <c r="N121" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.14508101851851851</v>
       </c>
       <c r="O121" s="41" t="s">
@@ -22105,13 +22624,16 @@
       <c r="AE121" s="56">
         <v>8.7962962962962962E-4</v>
       </c>
-      <c r="AF121" s="41"/>
-      <c r="AG121" s="41"/>
-      <c r="AH121" s="41"/>
-      <c r="AI121" s="41"/>
-      <c r="AJ121" s="41"/>
-    </row>
-    <row r="122" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF121" s="72"/>
+      <c r="AG121" s="72"/>
+      <c r="AH121" s="72"/>
+      <c r="AI121" s="72"/>
+      <c r="AJ121" s="72"/>
+      <c r="AK121" s="72"/>
+      <c r="AL121" s="72"/>
+      <c r="AM121" s="73"/>
+    </row>
+    <row r="122" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A122" s="41" t="s">
         <v>991</v>
       </c>
@@ -22152,7 +22674,7 @@
         <v>320</v>
       </c>
       <c r="N122" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.14577546296296295</v>
       </c>
       <c r="O122" s="41" t="s">
@@ -22186,15 +22708,15 @@
         <v>30</v>
       </c>
       <c r="Y122" s="43">
-        <f t="shared" ref="Y122:Y129" si="20">IF(ISNUMBER(X122),ROUND(X122*0.85,0),"—")</f>
+        <f t="shared" ref="Y122:Y129" si="22">IF(ISNUMBER(X122),ROUND(X122*0.85,0),"—")</f>
         <v>26</v>
       </c>
       <c r="Z122" s="43">
-        <f t="shared" ref="Z122:Z129" si="21">IF(ISNUMBER(X122),ROUND(X122*0.7,0),"—")</f>
+        <f t="shared" ref="Z122:Z129" si="23">IF(ISNUMBER(X122),ROUND(X122*0.7,0),"—")</f>
         <v>21</v>
       </c>
       <c r="AA122" s="43">
-        <f t="shared" ref="AA122:AA129" si="22">IF(ISNUMBER(X122),ROUND(X122*0.55,0),"—")</f>
+        <f t="shared" ref="AA122:AA129" si="24">IF(ISNUMBER(X122),ROUND(X122*0.55,0),"—")</f>
         <v>17</v>
       </c>
       <c r="AB122" s="56">
@@ -22209,13 +22731,16 @@
       <c r="AE122" s="56">
         <v>6.2500000000000001E-4</v>
       </c>
-      <c r="AF122" s="41"/>
-      <c r="AG122" s="41"/>
-      <c r="AH122" s="41"/>
-      <c r="AI122" s="41"/>
-      <c r="AJ122" s="41"/>
-    </row>
-    <row r="123" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF122" s="72"/>
+      <c r="AG122" s="72"/>
+      <c r="AH122" s="72"/>
+      <c r="AI122" s="72"/>
+      <c r="AJ122" s="72"/>
+      <c r="AK122" s="72"/>
+      <c r="AL122" s="72"/>
+      <c r="AM122" s="73"/>
+    </row>
+    <row r="123" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A123" s="41" t="s">
         <v>991</v>
       </c>
@@ -22256,7 +22781,7 @@
         <v>187</v>
       </c>
       <c r="N123" s="54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.14693287037037037</v>
       </c>
       <c r="O123" s="41" t="s">
@@ -22290,15 +22815,15 @@
         <v>20</v>
       </c>
       <c r="Y123" s="43">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
       <c r="Z123" s="43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>14</v>
       </c>
       <c r="AA123" s="43">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>11</v>
       </c>
       <c r="AB123" s="56">
@@ -22313,13 +22838,16 @@
       <c r="AE123" s="56">
         <v>1.0127314814814814E-3</v>
       </c>
-      <c r="AF123" s="41"/>
-      <c r="AG123" s="41"/>
-      <c r="AH123" s="41"/>
-      <c r="AI123" s="41"/>
-      <c r="AJ123" s="41"/>
-    </row>
-    <row r="124" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF123" s="72"/>
+      <c r="AG123" s="72"/>
+      <c r="AH123" s="72"/>
+      <c r="AI123" s="72"/>
+      <c r="AJ123" s="72"/>
+      <c r="AK123" s="72"/>
+      <c r="AL123" s="72"/>
+      <c r="AM123" s="73"/>
+    </row>
+    <row r="124" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A124" s="41" t="s">
         <v>991</v>
       </c>
@@ -22393,15 +22921,15 @@
         <v>120</v>
       </c>
       <c r="Y124" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>102</v>
       </c>
       <c r="Z124" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AA124" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="AB124" s="57">
@@ -22416,8 +22944,22 @@
       <c r="AE124" s="57">
         <v>1.9444444444444444E-3</v>
       </c>
-    </row>
-    <row r="125" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF124" s="72" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG124" s="72"/>
+      <c r="AH124" s="72" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI124" s="72"/>
+      <c r="AJ124" s="72"/>
+      <c r="AK124" s="72"/>
+      <c r="AL124" s="72"/>
+      <c r="AM124" s="75"/>
+    </row>
+    <row r="125" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A125" s="41" t="s">
         <v>991</v>
       </c>
@@ -22491,15 +23033,15 @@
         <v>100</v>
       </c>
       <c r="Y125" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>85</v>
       </c>
       <c r="Z125" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>70</v>
       </c>
       <c r="AA125" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>55</v>
       </c>
       <c r="AB125" s="57">
@@ -22514,8 +23056,16 @@
       <c r="AE125" s="57">
         <v>1.2037037037037036E-3</v>
       </c>
-    </row>
-    <row r="126" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF125" s="72"/>
+      <c r="AG125" s="72"/>
+      <c r="AH125" s="72"/>
+      <c r="AI125" s="72"/>
+      <c r="AJ125" s="72"/>
+      <c r="AK125" s="72"/>
+      <c r="AL125" s="72"/>
+      <c r="AM125" s="75"/>
+    </row>
+    <row r="126" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A126" s="48" t="s">
         <v>991</v>
       </c>
@@ -22589,15 +23139,15 @@
         <v>70</v>
       </c>
       <c r="Y126" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="Z126" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>49</v>
       </c>
       <c r="AA126" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>39</v>
       </c>
       <c r="AB126" s="57">
@@ -22612,8 +23162,16 @@
       <c r="AE126" s="57">
         <v>4.1666666666666664E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:36" ht="39.6" customHeight="1">
+      <c r="AF126" s="72"/>
+      <c r="AG126" s="72"/>
+      <c r="AH126" s="72"/>
+      <c r="AI126" s="72"/>
+      <c r="AJ126" s="72"/>
+      <c r="AK126" s="72"/>
+      <c r="AL126" s="72"/>
+      <c r="AM126" s="75"/>
+    </row>
+    <row r="127" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A127" s="48" t="s">
         <v>991</v>
       </c>
@@ -22687,15 +23245,15 @@
         <v>150</v>
       </c>
       <c r="Y127" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>128</v>
       </c>
       <c r="Z127" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>105</v>
       </c>
       <c r="AA127" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>83</v>
       </c>
       <c r="AB127" s="57">
@@ -22710,8 +23268,22 @@
       <c r="AE127" s="57">
         <v>2.1527777777777778E-3</v>
       </c>
-    </row>
-    <row r="128" spans="1:36" ht="26.45" customHeight="1">
+      <c r="AF127" s="72" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG127" s="72"/>
+      <c r="AH127" s="72" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI127" s="72"/>
+      <c r="AJ127" s="72"/>
+      <c r="AK127" s="72"/>
+      <c r="AL127" s="72"/>
+      <c r="AM127" s="75"/>
+    </row>
+    <row r="128" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A128" s="48" t="s">
         <v>991</v>
       </c>
@@ -22785,15 +23357,15 @@
         <v>120</v>
       </c>
       <c r="Y128" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>102</v>
       </c>
       <c r="Z128" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AA128" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="AB128" s="57">
@@ -22808,8 +23380,16 @@
       <c r="AE128" s="57">
         <v>1.3888888888888889E-3</v>
       </c>
-    </row>
-    <row r="129" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF128" s="72"/>
+      <c r="AG128" s="72"/>
+      <c r="AH128" s="72"/>
+      <c r="AI128" s="72"/>
+      <c r="AJ128" s="72"/>
+      <c r="AK128" s="72"/>
+      <c r="AL128" s="72"/>
+      <c r="AM128" s="75"/>
+    </row>
+    <row r="129" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A129" s="48" t="s">
         <v>991</v>
       </c>
@@ -22883,15 +23463,15 @@
         <v>50</v>
       </c>
       <c r="Y129" s="49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>43</v>
       </c>
       <c r="Z129" s="49">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>35</v>
       </c>
       <c r="AA129" s="49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
       <c r="AB129" s="57">
@@ -22906,8 +23486,16 @@
       <c r="AE129" s="57">
         <v>1.3368055555555555E-3</v>
       </c>
-    </row>
-    <row r="130" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF129" s="72"/>
+      <c r="AG129" s="72"/>
+      <c r="AH129" s="72"/>
+      <c r="AI129" s="72"/>
+      <c r="AJ129" s="72"/>
+      <c r="AK129" s="72"/>
+      <c r="AL129" s="72"/>
+      <c r="AM129" s="75"/>
+    </row>
+    <row r="130" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A130" s="48" t="s">
         <v>991</v>
       </c>
@@ -23001,8 +23589,16 @@
       <c r="AE130" s="57">
         <v>9.895833333333332E-4</v>
       </c>
-    </row>
-    <row r="131" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF130" s="72"/>
+      <c r="AG130" s="72"/>
+      <c r="AH130" s="72"/>
+      <c r="AI130" s="72"/>
+      <c r="AJ130" s="72"/>
+      <c r="AK130" s="72"/>
+      <c r="AL130" s="72"/>
+      <c r="AM130" s="75"/>
+    </row>
+    <row r="131" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A131" s="48" t="s">
         <v>991</v>
       </c>
@@ -23099,8 +23695,16 @@
       <c r="AE131" s="57">
         <v>1.5393518518518516E-3</v>
       </c>
-    </row>
-    <row r="132" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF131" s="72"/>
+      <c r="AG131" s="72"/>
+      <c r="AH131" s="72"/>
+      <c r="AI131" s="72"/>
+      <c r="AJ131" s="72"/>
+      <c r="AK131" s="72"/>
+      <c r="AL131" s="72"/>
+      <c r="AM131" s="75"/>
+    </row>
+    <row r="132" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A132" s="48" t="s">
         <v>991</v>
       </c>
@@ -23197,8 +23801,16 @@
       <c r="AE132" s="57">
         <v>1.7708333333333332E-3</v>
       </c>
-    </row>
-    <row r="133" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF132" s="72"/>
+      <c r="AG132" s="72"/>
+      <c r="AH132" s="72"/>
+      <c r="AI132" s="72"/>
+      <c r="AJ132" s="72"/>
+      <c r="AK132" s="72"/>
+      <c r="AL132" s="72"/>
+      <c r="AM132" s="75"/>
+    </row>
+    <row r="133" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A133" s="48" t="s">
         <v>991</v>
       </c>
@@ -23292,8 +23904,16 @@
       <c r="AE133" s="57">
         <v>1.2094907407407408E-3</v>
       </c>
-    </row>
-    <row r="134" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF133" s="72"/>
+      <c r="AG133" s="72"/>
+      <c r="AH133" s="72"/>
+      <c r="AI133" s="72"/>
+      <c r="AJ133" s="72"/>
+      <c r="AK133" s="72"/>
+      <c r="AL133" s="72"/>
+      <c r="AM133" s="75"/>
+    </row>
+    <row r="134" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A134" s="48" t="s">
         <v>948</v>
       </c>
@@ -23387,8 +24007,16 @@
       <c r="AE134" s="57">
         <v>1.0995370370370369E-3</v>
       </c>
-    </row>
-    <row r="135" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF134" s="72"/>
+      <c r="AG134" s="72"/>
+      <c r="AH134" s="72"/>
+      <c r="AI134" s="72"/>
+      <c r="AJ134" s="72"/>
+      <c r="AK134" s="72"/>
+      <c r="AL134" s="72"/>
+      <c r="AM134" s="75"/>
+    </row>
+    <row r="135" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A135" s="48" t="s">
         <v>948</v>
       </c>
@@ -23482,8 +24110,16 @@
       <c r="AE135" s="57">
         <v>1.5393518518518516E-3</v>
       </c>
-    </row>
-    <row r="136" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF135" s="72"/>
+      <c r="AG135" s="72"/>
+      <c r="AH135" s="72"/>
+      <c r="AI135" s="72"/>
+      <c r="AJ135" s="72"/>
+      <c r="AK135" s="72"/>
+      <c r="AL135" s="72"/>
+      <c r="AM135" s="75"/>
+    </row>
+    <row r="136" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A136" s="48" t="s">
         <v>948</v>
       </c>
@@ -23557,15 +24193,15 @@
         <v>20</v>
       </c>
       <c r="Y136" s="49">
-        <f t="shared" ref="Y136:Y143" si="23">IF(ISNUMBER(X136),ROUND(X136*0.85,0),"—")</f>
+        <f t="shared" ref="Y136:Y143" si="25">IF(ISNUMBER(X136),ROUND(X136*0.85,0),"—")</f>
         <v>17</v>
       </c>
       <c r="Z136" s="49">
-        <f t="shared" ref="Z136:Z143" si="24">IF(ISNUMBER(X136),ROUND(X136*0.7,0),"—")</f>
+        <f t="shared" ref="Z136:Z143" si="26">IF(ISNUMBER(X136),ROUND(X136*0.7,0),"—")</f>
         <v>14</v>
       </c>
       <c r="AA136" s="49">
-        <f t="shared" ref="AA136:AA143" si="25">IF(ISNUMBER(X136),ROUND(X136*0.55,0),"—")</f>
+        <f t="shared" ref="AA136:AA143" si="27">IF(ISNUMBER(X136),ROUND(X136*0.55,0),"—")</f>
         <v>11</v>
       </c>
       <c r="AB136" s="57">
@@ -23580,8 +24216,16 @@
       <c r="AE136" s="57">
         <v>1.8229166666666667E-3</v>
       </c>
-    </row>
-    <row r="137" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF136" s="72"/>
+      <c r="AG136" s="72"/>
+      <c r="AH136" s="72"/>
+      <c r="AI136" s="72"/>
+      <c r="AJ136" s="72"/>
+      <c r="AK136" s="72"/>
+      <c r="AL136" s="72"/>
+      <c r="AM136" s="75"/>
+    </row>
+    <row r="137" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A137" s="48" t="s">
         <v>948</v>
       </c>
@@ -23655,15 +24299,15 @@
         <v>50</v>
       </c>
       <c r="Y137" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>43</v>
       </c>
       <c r="Z137" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>35</v>
       </c>
       <c r="AA137" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>28</v>
       </c>
       <c r="AB137" s="57">
@@ -23678,8 +24322,16 @@
       <c r="AE137" s="57">
         <v>1.2789351851851853E-3</v>
       </c>
-    </row>
-    <row r="138" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF137" s="72"/>
+      <c r="AG137" s="72"/>
+      <c r="AH137" s="72"/>
+      <c r="AI137" s="72"/>
+      <c r="AJ137" s="72"/>
+      <c r="AK137" s="72"/>
+      <c r="AL137" s="72"/>
+      <c r="AM137" s="75"/>
+    </row>
+    <row r="138" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A138" s="48" t="s">
         <v>948</v>
       </c>
@@ -23753,15 +24405,15 @@
         <v>50</v>
       </c>
       <c r="Y138" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>43</v>
       </c>
       <c r="Z138" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>35</v>
       </c>
       <c r="AA138" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>28</v>
       </c>
       <c r="AB138" s="57">
@@ -23776,8 +24428,16 @@
       <c r="AE138" s="57">
         <v>2.2280092592592594E-3</v>
       </c>
-    </row>
-    <row r="139" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF138" s="72"/>
+      <c r="AG138" s="72"/>
+      <c r="AH138" s="72"/>
+      <c r="AI138" s="72"/>
+      <c r="AJ138" s="72"/>
+      <c r="AK138" s="72"/>
+      <c r="AL138" s="72"/>
+      <c r="AM138" s="75"/>
+    </row>
+    <row r="139" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A139" s="48" t="s">
         <v>948</v>
       </c>
@@ -23851,15 +24511,15 @@
         <v>30</v>
       </c>
       <c r="Y139" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>26</v>
       </c>
       <c r="Z139" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>21</v>
       </c>
       <c r="AA139" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17</v>
       </c>
       <c r="AB139" s="57">
@@ -23874,8 +24534,16 @@
       <c r="AE139" s="57">
         <v>2.3090277777777779E-3</v>
       </c>
-    </row>
-    <row r="140" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF139" s="72"/>
+      <c r="AG139" s="72"/>
+      <c r="AH139" s="72"/>
+      <c r="AI139" s="72"/>
+      <c r="AJ139" s="72"/>
+      <c r="AK139" s="72"/>
+      <c r="AL139" s="72"/>
+      <c r="AM139" s="75"/>
+    </row>
+    <row r="140" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A140" s="48" t="s">
         <v>948</v>
       </c>
@@ -23949,15 +24617,15 @@
         <v>100</v>
       </c>
       <c r="Y140" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>85</v>
       </c>
       <c r="Z140" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
       <c r="AA140" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>55</v>
       </c>
       <c r="AB140" s="57">
@@ -23972,8 +24640,22 @@
       <c r="AE140" s="57">
         <v>2.4826388888888888E-3</v>
       </c>
-    </row>
-    <row r="141" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF140" s="72" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG140" s="72"/>
+      <c r="AH140" s="72" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI140" s="72"/>
+      <c r="AJ140" s="72"/>
+      <c r="AK140" s="72"/>
+      <c r="AL140" s="72"/>
+      <c r="AM140" s="75"/>
+    </row>
+    <row r="141" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A141" s="48" t="s">
         <v>948</v>
       </c>
@@ -24047,15 +24729,15 @@
         <v>100</v>
       </c>
       <c r="Y141" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>85</v>
       </c>
       <c r="Z141" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
       <c r="AA141" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>55</v>
       </c>
       <c r="AB141" s="57">
@@ -24070,8 +24752,16 @@
       <c r="AE141" s="57">
         <v>1.8142361111111111E-3</v>
       </c>
-    </row>
-    <row r="142" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF141" s="72"/>
+      <c r="AG141" s="72"/>
+      <c r="AH141" s="72"/>
+      <c r="AI141" s="72"/>
+      <c r="AJ141" s="72"/>
+      <c r="AK141" s="72"/>
+      <c r="AL141" s="72"/>
+      <c r="AM141" s="75"/>
+    </row>
+    <row r="142" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A142" s="48" t="s">
         <v>948</v>
       </c>
@@ -24145,15 +24835,15 @@
         <v>150</v>
       </c>
       <c r="Y142" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>128</v>
       </c>
       <c r="Z142" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>105</v>
       </c>
       <c r="AA142" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>83</v>
       </c>
       <c r="AB142" s="57">
@@ -24168,8 +24858,26 @@
       <c r="AE142" s="57">
         <v>1.7939814814814813E-3</v>
       </c>
-    </row>
-    <row r="143" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF142" s="74" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG142" s="74">
+        <v>1</v>
+      </c>
+      <c r="AH142" s="74" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AI142" s="74">
+        <v>210</v>
+      </c>
+      <c r="AJ142" s="74"/>
+      <c r="AK142" s="74"/>
+      <c r="AL142" s="74"/>
+      <c r="AM142" s="75"/>
+    </row>
+    <row r="143" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A143" s="48" t="s">
         <v>948</v>
       </c>
@@ -24243,15 +24951,15 @@
         <v>50</v>
       </c>
       <c r="Y143" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>43</v>
       </c>
       <c r="Z143" s="49">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>35</v>
       </c>
       <c r="AA143" s="49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>28</v>
       </c>
       <c r="AB143" s="57">
@@ -24266,8 +24974,16 @@
       <c r="AE143" s="57">
         <v>1.4756944444444444E-3</v>
       </c>
-    </row>
-    <row r="144" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF143" s="72"/>
+      <c r="AG143" s="72"/>
+      <c r="AH143" s="72"/>
+      <c r="AI143" s="72"/>
+      <c r="AJ143" s="72"/>
+      <c r="AK143" s="72"/>
+      <c r="AL143" s="72"/>
+      <c r="AM143" s="75"/>
+    </row>
+    <row r="144" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A144" s="48" t="s">
         <v>948</v>
       </c>
@@ -24361,8 +25077,16 @@
       <c r="AE144" s="57">
         <v>2.0891203703703705E-3</v>
       </c>
-    </row>
-    <row r="145" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF144" s="72"/>
+      <c r="AG144" s="72"/>
+      <c r="AH144" s="72"/>
+      <c r="AI144" s="72"/>
+      <c r="AJ144" s="72"/>
+      <c r="AK144" s="72"/>
+      <c r="AL144" s="72"/>
+      <c r="AM144" s="75"/>
+    </row>
+    <row r="145" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A145" s="48" t="s">
         <v>948</v>
       </c>
@@ -24456,8 +25180,16 @@
       <c r="AE145" s="57">
         <v>1.7592592592592592E-3</v>
       </c>
-    </row>
-    <row r="146" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF145" s="72"/>
+      <c r="AG145" s="72"/>
+      <c r="AH145" s="72"/>
+      <c r="AI145" s="72"/>
+      <c r="AJ145" s="72"/>
+      <c r="AK145" s="72"/>
+      <c r="AL145" s="72"/>
+      <c r="AM145" s="75"/>
+    </row>
+    <row r="146" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A146" s="48" t="s">
         <v>948</v>
       </c>
@@ -24554,8 +25286,16 @@
       <c r="AE146" s="57">
         <v>1.6493055555555553E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF146" s="72"/>
+      <c r="AG146" s="72"/>
+      <c r="AH146" s="72"/>
+      <c r="AI146" s="72"/>
+      <c r="AJ146" s="72"/>
+      <c r="AK146" s="72"/>
+      <c r="AL146" s="72"/>
+      <c r="AM146" s="75"/>
+    </row>
+    <row r="147" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A147" s="48" t="s">
         <v>948</v>
       </c>
@@ -24652,8 +25392,16 @@
       <c r="AE147" s="57">
         <v>2.0833333333333329E-3</v>
       </c>
-    </row>
-    <row r="148" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF147" s="72"/>
+      <c r="AG147" s="72"/>
+      <c r="AH147" s="72"/>
+      <c r="AI147" s="72"/>
+      <c r="AJ147" s="72"/>
+      <c r="AK147" s="72"/>
+      <c r="AL147" s="72"/>
+      <c r="AM147" s="75"/>
+    </row>
+    <row r="148" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A148" s="48" t="s">
         <v>948</v>
       </c>
@@ -24750,8 +25498,16 @@
       <c r="AE148" s="57">
         <v>1.7187499999999998E-3</v>
       </c>
-    </row>
-    <row r="149" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF148" s="72"/>
+      <c r="AG148" s="72"/>
+      <c r="AH148" s="72"/>
+      <c r="AI148" s="72"/>
+      <c r="AJ148" s="72"/>
+      <c r="AK148" s="72"/>
+      <c r="AL148" s="72"/>
+      <c r="AM148" s="75"/>
+    </row>
+    <row r="149" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A149" s="48" t="s">
         <v>948</v>
       </c>
@@ -24848,8 +25604,16 @@
       <c r="AE149" s="57">
         <v>2.1643518518518518E-3</v>
       </c>
-    </row>
-    <row r="150" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF149" s="72"/>
+      <c r="AG149" s="72"/>
+      <c r="AH149" s="72"/>
+      <c r="AI149" s="72"/>
+      <c r="AJ149" s="72"/>
+      <c r="AK149" s="72"/>
+      <c r="AL149" s="72"/>
+      <c r="AM149" s="75"/>
+    </row>
+    <row r="150" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A150" s="48" t="s">
         <v>948</v>
       </c>
@@ -24946,8 +25710,16 @@
       <c r="AE150" s="57">
         <v>1.3194444444444445E-3</v>
       </c>
-    </row>
-    <row r="151" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF150" s="72"/>
+      <c r="AG150" s="72"/>
+      <c r="AH150" s="72"/>
+      <c r="AI150" s="72"/>
+      <c r="AJ150" s="72"/>
+      <c r="AK150" s="72"/>
+      <c r="AL150" s="72"/>
+      <c r="AM150" s="75"/>
+    </row>
+    <row r="151" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A151" s="48" t="s">
         <v>948</v>
       </c>
@@ -25041,8 +25813,16 @@
       <c r="AE151" s="57">
         <v>1.6493055555555553E-3</v>
       </c>
-    </row>
-    <row r="152" spans="1:31" ht="39.6" customHeight="1">
+      <c r="AF151" s="72"/>
+      <c r="AG151" s="72"/>
+      <c r="AH151" s="72"/>
+      <c r="AI151" s="72"/>
+      <c r="AJ151" s="72"/>
+      <c r="AK151" s="72"/>
+      <c r="AL151" s="72"/>
+      <c r="AM151" s="75"/>
+    </row>
+    <row r="152" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A152" s="48" t="s">
         <v>948</v>
       </c>
@@ -25139,8 +25919,16 @@
       <c r="AE152" s="57">
         <v>2.638888888888889E-3</v>
       </c>
-    </row>
-    <row r="153" spans="1:31" ht="26.45" customHeight="1">
+      <c r="AF152" s="72"/>
+      <c r="AG152" s="72"/>
+      <c r="AH152" s="72"/>
+      <c r="AI152" s="72"/>
+      <c r="AJ152" s="72"/>
+      <c r="AK152" s="72"/>
+      <c r="AL152" s="72"/>
+      <c r="AM152" s="75"/>
+    </row>
+    <row r="153" spans="1:39" ht="65.099999999999994" customHeight="1">
       <c r="A153" s="48" t="s">
         <v>948</v>
       </c>
@@ -25234,6 +26022,272 @@
       <c r="AE153" s="57">
         <v>1.9791666666666664E-3</v>
       </c>
+      <c r="AF153" s="72"/>
+      <c r="AG153" s="72"/>
+      <c r="AH153" s="72"/>
+      <c r="AI153" s="72"/>
+      <c r="AJ153" s="72"/>
+      <c r="AK153" s="72"/>
+      <c r="AL153" s="72"/>
+      <c r="AM153" s="75"/>
+    </row>
+    <row r="154" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF154" s="72"/>
+      <c r="AG154" s="72"/>
+      <c r="AH154" s="72"/>
+      <c r="AI154" s="72"/>
+      <c r="AJ154" s="72"/>
+      <c r="AK154" s="72"/>
+      <c r="AL154" s="72"/>
+      <c r="AM154" s="75"/>
+    </row>
+    <row r="155" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF155" s="72"/>
+      <c r="AG155" s="72"/>
+      <c r="AH155" s="72"/>
+      <c r="AI155" s="72"/>
+      <c r="AJ155" s="72"/>
+      <c r="AK155" s="72"/>
+      <c r="AL155" s="72"/>
+      <c r="AM155" s="75"/>
+    </row>
+    <row r="156" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF156" s="72"/>
+      <c r="AG156" s="72"/>
+      <c r="AH156" s="72"/>
+      <c r="AI156" s="72"/>
+      <c r="AJ156" s="72"/>
+      <c r="AK156" s="72"/>
+      <c r="AL156" s="72"/>
+      <c r="AM156" s="75"/>
+    </row>
+    <row r="157" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF157" s="72"/>
+      <c r="AG157" s="72"/>
+      <c r="AH157" s="72"/>
+      <c r="AI157" s="72"/>
+      <c r="AJ157" s="72"/>
+      <c r="AK157" s="72"/>
+      <c r="AL157" s="72"/>
+      <c r="AM157" s="75"/>
+    </row>
+    <row r="158" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF158" s="72"/>
+      <c r="AG158" s="72"/>
+      <c r="AH158" s="72"/>
+      <c r="AI158" s="72"/>
+      <c r="AJ158" s="72"/>
+      <c r="AK158" s="72"/>
+      <c r="AL158" s="72"/>
+      <c r="AM158" s="75"/>
+    </row>
+    <row r="159" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF159" s="72"/>
+      <c r="AG159" s="72"/>
+      <c r="AH159" s="72"/>
+      <c r="AI159" s="72"/>
+      <c r="AJ159" s="72"/>
+      <c r="AK159" s="72"/>
+      <c r="AL159" s="72"/>
+      <c r="AM159" s="75"/>
+    </row>
+    <row r="160" spans="1:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF160" s="72"/>
+      <c r="AG160" s="72"/>
+      <c r="AH160" s="72"/>
+      <c r="AI160" s="72"/>
+      <c r="AJ160" s="72"/>
+      <c r="AK160" s="72"/>
+      <c r="AL160" s="72"/>
+      <c r="AM160" s="75"/>
+    </row>
+    <row r="161" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF161" s="72"/>
+      <c r="AG161" s="72"/>
+      <c r="AH161" s="72"/>
+      <c r="AI161" s="72"/>
+      <c r="AJ161" s="72"/>
+      <c r="AK161" s="72"/>
+      <c r="AL161" s="72"/>
+      <c r="AM161" s="75"/>
+    </row>
+    <row r="162" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF162" s="72"/>
+      <c r="AG162" s="72"/>
+      <c r="AH162" s="72"/>
+      <c r="AI162" s="72"/>
+      <c r="AJ162" s="72"/>
+      <c r="AK162" s="72"/>
+      <c r="AL162" s="72"/>
+      <c r="AM162" s="75"/>
+    </row>
+    <row r="163" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF163" s="74">
+        <v>1500</v>
+      </c>
+      <c r="AG163" s="74">
+        <v>1</v>
+      </c>
+      <c r="AH163" s="74">
+        <v>180</v>
+      </c>
+      <c r="AI163" s="74">
+        <v>390</v>
+      </c>
+      <c r="AJ163" s="74"/>
+      <c r="AK163" s="74"/>
+      <c r="AL163" s="74"/>
+      <c r="AM163" s="75"/>
+    </row>
+    <row r="164" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF164" s="72"/>
+      <c r="AG164" s="72"/>
+      <c r="AH164" s="72"/>
+      <c r="AI164" s="72"/>
+      <c r="AJ164" s="72"/>
+      <c r="AK164" s="72"/>
+      <c r="AL164" s="72"/>
+      <c r="AM164" s="75"/>
+    </row>
+    <row r="165" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF165" s="72"/>
+      <c r="AG165" s="72"/>
+      <c r="AH165" s="72"/>
+      <c r="AI165" s="72"/>
+      <c r="AJ165" s="72"/>
+      <c r="AK165" s="72"/>
+      <c r="AL165" s="72"/>
+      <c r="AM165" s="75"/>
+    </row>
+    <row r="166" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF166" s="72"/>
+      <c r="AG166" s="72"/>
+      <c r="AH166" s="72"/>
+      <c r="AI166" s="72"/>
+      <c r="AJ166" s="72"/>
+      <c r="AK166" s="72"/>
+      <c r="AL166" s="72"/>
+      <c r="AM166" s="75"/>
+    </row>
+    <row r="167" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF167" s="72"/>
+      <c r="AG167" s="72"/>
+      <c r="AH167" s="72"/>
+      <c r="AI167" s="72"/>
+      <c r="AJ167" s="72"/>
+      <c r="AK167" s="72"/>
+      <c r="AL167" s="72"/>
+      <c r="AM167" s="75"/>
+    </row>
+    <row r="168" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF168" s="72"/>
+      <c r="AG168" s="72"/>
+      <c r="AH168" s="72"/>
+      <c r="AI168" s="72"/>
+      <c r="AJ168" s="72"/>
+      <c r="AK168" s="72"/>
+      <c r="AL168" s="72"/>
+      <c r="AM168" s="75"/>
+    </row>
+    <row r="169" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF169" s="72"/>
+      <c r="AG169" s="72"/>
+      <c r="AH169" s="72"/>
+      <c r="AI169" s="72"/>
+      <c r="AJ169" s="72"/>
+      <c r="AK169" s="72"/>
+      <c r="AL169" s="72"/>
+      <c r="AM169" s="75"/>
+    </row>
+    <row r="170" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF170" s="72"/>
+      <c r="AG170" s="72"/>
+      <c r="AH170" s="72"/>
+      <c r="AI170" s="72"/>
+      <c r="AJ170" s="72"/>
+      <c r="AK170" s="72"/>
+      <c r="AL170" s="72"/>
+      <c r="AM170" s="75"/>
+    </row>
+    <row r="171" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF171" s="72"/>
+      <c r="AG171" s="72"/>
+      <c r="AH171" s="72"/>
+      <c r="AI171" s="72"/>
+      <c r="AJ171" s="72"/>
+      <c r="AK171" s="72"/>
+      <c r="AL171" s="72"/>
+      <c r="AM171" s="75"/>
+    </row>
+    <row r="172" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF172" s="72"/>
+      <c r="AG172" s="72"/>
+      <c r="AH172" s="72"/>
+      <c r="AI172" s="72"/>
+      <c r="AJ172" s="72"/>
+      <c r="AK172" s="72"/>
+      <c r="AL172" s="72"/>
+      <c r="AM172" s="75"/>
+    </row>
+    <row r="173" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF173" s="72"/>
+      <c r="AG173" s="72"/>
+      <c r="AH173" s="72"/>
+      <c r="AI173" s="72"/>
+      <c r="AJ173" s="72"/>
+      <c r="AK173" s="72"/>
+      <c r="AL173" s="72"/>
+      <c r="AM173" s="75"/>
+    </row>
+    <row r="174" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF174" s="72"/>
+      <c r="AG174" s="72"/>
+      <c r="AH174" s="72"/>
+      <c r="AI174" s="72"/>
+      <c r="AJ174" s="72"/>
+      <c r="AK174" s="72"/>
+      <c r="AL174" s="72"/>
+      <c r="AM174" s="75"/>
+    </row>
+    <row r="175" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF175" s="72"/>
+      <c r="AG175" s="72"/>
+      <c r="AH175" s="72"/>
+      <c r="AI175" s="72"/>
+      <c r="AJ175" s="72"/>
+      <c r="AK175" s="72"/>
+      <c r="AL175" s="72"/>
+      <c r="AM175" s="75"/>
+    </row>
+    <row r="176" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF176" s="72"/>
+      <c r="AG176" s="72"/>
+      <c r="AH176" s="72"/>
+      <c r="AI176" s="72"/>
+      <c r="AJ176" s="72"/>
+      <c r="AK176" s="72"/>
+      <c r="AL176" s="72"/>
+      <c r="AM176" s="75"/>
+    </row>
+    <row r="177" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF177" s="72"/>
+      <c r="AG177" s="72"/>
+      <c r="AH177" s="72"/>
+      <c r="AI177" s="72"/>
+      <c r="AJ177" s="72"/>
+      <c r="AK177" s="72"/>
+      <c r="AL177" s="72"/>
+      <c r="AM177" s="75"/>
+    </row>
+    <row r="178" spans="32:39" ht="65.099999999999994" customHeight="1">
+      <c r="AF178" s="72"/>
+      <c r="AG178" s="72"/>
+      <c r="AH178" s="72"/>
+      <c r="AI178" s="72"/>
+      <c r="AJ178" s="72"/>
+      <c r="AK178" s="72"/>
+      <c r="AL178" s="72"/>
+      <c r="AM178" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="3">
